--- a/dev_Python/3. 투자/4. 개별종목분석/1. rxrx/RXRX_bollinger_analysis.xlsx
+++ b/dev_Python/3. 투자/4. 개별종목분석/1. rxrx/RXRX_bollinger_analysis.xlsx
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.390000104904175</v>
+        <v>3.420000076293945</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.0191317842653</v>
+        <v>15.18623094103658</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40.4096868236392</v>
+        <v>41.70380785416495</v>
       </c>
     </row>
     <row r="8">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5826738367437813</v>
+        <v>0.5973323120397694</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.89184337162819</v>
+        <v>14.47826330987637</v>
       </c>
       <c r="C2" t="n">
-        <v>15.0191317842653</v>
+        <v>15.18623094103658</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.872711587362888</v>
+        <v>0.7079676311602139</v>
       </c>
       <c r="E2" t="n">
-        <v>-11.0864844420019</v>
+        <v>4.889865697340045</v>
       </c>
     </row>
     <row r="3">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.4595666552202</v>
+        <v>21.86746849295706</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0191317842653</v>
+        <v>15.18623094103658</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.440434870954904</v>
+        <v>-6.681237551920479</v>
       </c>
       <c r="E3" t="n">
-        <v>-38.59608391279536</v>
+        <v>-30.55331966785424</v>
       </c>
     </row>
     <row r="4">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.32949162540094</v>
+        <v>38.06883322015099</v>
       </c>
       <c r="C4" t="n">
-        <v>15.0191317842653</v>
+        <v>15.18623094103658</v>
       </c>
       <c r="D4" t="n">
-        <v>-25.31035984113564</v>
+        <v>-22.8826022791144</v>
       </c>
       <c r="E4" t="n">
-        <v>-62.75893600700457</v>
+        <v>-60.1084938610673</v>
       </c>
     </row>
     <row r="5">
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.19616549613495</v>
+        <v>43.17856736740559</v>
       </c>
       <c r="C5" t="n">
-        <v>15.0191317842653</v>
+        <v>15.18623094103658</v>
       </c>
       <c r="D5" t="n">
-        <v>-26.17703371186965</v>
+        <v>-27.99233642636901</v>
       </c>
       <c r="E5" t="n">
-        <v>-63.54240351404938</v>
+        <v>-64.82923851591175</v>
       </c>
     </row>
   </sheetData>
@@ -958,83 +958,83 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B2" t="n">
-        <v>4.510000228881836</v>
+        <v>4.760000228881836</v>
       </c>
       <c r="C2" t="n">
-        <v>5.010000228881836</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="D2" t="n">
-        <v>4.480000019073486</v>
+        <v>4.440000057220459</v>
       </c>
       <c r="E2" t="n">
-        <v>4.679999828338623</v>
+        <v>4.440000057220459</v>
       </c>
       <c r="F2" t="n">
-        <v>65554800</v>
+        <v>31684800</v>
       </c>
       <c r="G2" t="n">
-        <v>4.397999858856201</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="H2" t="n">
-        <v>4.455499982833862</v>
+        <v>4.475999975204468</v>
       </c>
       <c r="I2" t="n">
-        <v>5.04283332824707</v>
+        <v>5.035499993960062</v>
       </c>
       <c r="J2" t="n">
-        <v>5.164166653156281</v>
+        <v>5.158999987443289</v>
       </c>
       <c r="K2" t="n">
-        <v>5.622499993443489</v>
+        <v>5.608499992887179</v>
       </c>
       <c r="L2" t="n">
-        <v>4.455499982833862</v>
+        <v>4.475999975204468</v>
       </c>
       <c r="M2" t="n">
-        <v>5.031784846776484</v>
+        <v>5.016619572576894</v>
       </c>
       <c r="N2" t="n">
-        <v>3.87921511889124</v>
+        <v>3.935380377832042</v>
       </c>
       <c r="O2" t="n">
-        <v>51.48994431545336</v>
+        <v>46.75528560944818</v>
       </c>
       <c r="P2" t="n">
-        <v>25.86847115533299</v>
+        <v>24.15637177691136</v>
       </c>
       <c r="Q2" t="n">
-        <v>22465940</v>
+        <v>22658345</v>
       </c>
       <c r="R2" t="n">
-        <v>2.91796381544685</v>
+        <v>1.398372211209601</v>
       </c>
       <c r="S2" t="n">
-        <v>11.42857240170854</v>
+        <v>-5.128200425668883</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.344119939890092</v>
+        <v>-1.712099378421634</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.312803982788269</v>
+        <v>-6.618479183176118</v>
       </c>
       <c r="V2" t="n">
-        <v>8.083138817540746</v>
+        <v>5.714291877487354</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.886795659282359</v>
+        <v>-3.056765694710106</v>
       </c>
       <c r="X2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="b">
         <v>0</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Bullish-neutral</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AA2" t="b">
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>28.33333333333333</v>
+        <v>25</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="b">
         <v>0</v>
@@ -1076,22 +1076,22 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Bullish trend bias</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AR2" t="b">
@@ -1108,79 +1108,79 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>Bullish trend bias</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B3" t="n">
-        <v>4.760000228881836</v>
+        <v>4.510000228881836</v>
       </c>
       <c r="C3" t="n">
-        <v>4.960000038146973</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="D3" t="n">
-        <v>4.440000057220459</v>
+        <v>4.25</v>
       </c>
       <c r="E3" t="n">
-        <v>4.440000057220459</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="F3" t="n">
-        <v>31684800</v>
+        <v>55008600</v>
       </c>
       <c r="G3" t="n">
-        <v>4.369999885559082</v>
+        <v>4.355999946594238</v>
       </c>
       <c r="H3" t="n">
-        <v>4.475999975204468</v>
+        <v>4.496499991416931</v>
       </c>
       <c r="I3" t="n">
-        <v>5.035499993960062</v>
+        <v>5.029333329200744</v>
       </c>
       <c r="J3" t="n">
-        <v>5.158999987443289</v>
+        <v>5.151749988396962</v>
       </c>
       <c r="K3" t="n">
-        <v>5.608499992887179</v>
+        <v>5.593124994635582</v>
       </c>
       <c r="L3" t="n">
-        <v>4.475999975204468</v>
+        <v>4.496499991416931</v>
       </c>
       <c r="M3" t="n">
-        <v>5.016619572576894</v>
+        <v>4.963214182513303</v>
       </c>
       <c r="N3" t="n">
-        <v>3.935380377832042</v>
+        <v>4.029785800320559</v>
       </c>
       <c r="O3" t="n">
-        <v>46.75528560944818</v>
+        <v>43.52285244336286</v>
       </c>
       <c r="P3" t="n">
-        <v>24.15637177691136</v>
+        <v>20.75899886521747</v>
       </c>
       <c r="Q3" t="n">
-        <v>22658345</v>
+        <v>23466975</v>
       </c>
       <c r="R3" t="n">
-        <v>1.398372211209601</v>
+        <v>2.344085677851534</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.128200425668883</v>
+        <v>-4.054050135560294</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.712099378421634</v>
+        <v>-3.397372911693886</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.618479183176118</v>
+        <v>-14.06408604350547</v>
       </c>
       <c r="V3" t="n">
-        <v>5.714291877487354</v>
+        <v>1.428581484321478</v>
       </c>
       <c r="W3" t="n">
-        <v>-3.056765694710106</v>
+        <v>-1.616621156064735</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish-neutral</t>
         </is>
       </c>
       <c r="AA3" t="b">
@@ -1200,7 +1200,7 @@
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -1232,22 +1232,22 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
       <c r="AR3" t="b">
@@ -1264,79 +1264,79 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B4" t="n">
-        <v>4.510000228881836</v>
+        <v>4.360000133514404</v>
       </c>
       <c r="C4" t="n">
         <v>4.53000020980835</v>
       </c>
       <c r="D4" t="n">
-        <v>4.25</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="E4" t="n">
-        <v>4.260000228881836</v>
+        <v>4.400000095367432</v>
       </c>
       <c r="F4" t="n">
-        <v>55008600</v>
+        <v>24629000</v>
       </c>
       <c r="G4" t="n">
-        <v>4.355999946594238</v>
+        <v>4.396000003814697</v>
       </c>
       <c r="H4" t="n">
-        <v>4.496499991416931</v>
+        <v>4.507999992370605</v>
       </c>
       <c r="I4" t="n">
-        <v>5.029333329200744</v>
+        <v>5.024000000953674</v>
       </c>
       <c r="J4" t="n">
-        <v>5.151749988396962</v>
+        <v>5.1449999888738</v>
       </c>
       <c r="K4" t="n">
-        <v>5.593124994635582</v>
+        <v>5.580249995986621</v>
       </c>
       <c r="L4" t="n">
-        <v>4.496499991416931</v>
+        <v>4.507999992370605</v>
       </c>
       <c r="M4" t="n">
-        <v>4.963214182513303</v>
+        <v>4.951602512826302</v>
       </c>
       <c r="N4" t="n">
-        <v>4.029785800320559</v>
+        <v>4.064397471914909</v>
       </c>
       <c r="O4" t="n">
-        <v>43.52285244336286</v>
+        <v>46.61431421053037</v>
       </c>
       <c r="P4" t="n">
-        <v>20.75899886521747</v>
+        <v>19.68067973409294</v>
       </c>
       <c r="Q4" t="n">
-        <v>23466975</v>
+        <v>23016805</v>
       </c>
       <c r="R4" t="n">
-        <v>2.344085677851534</v>
+        <v>1.070044256794112</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.054050135560294</v>
+        <v>3.286381665813742</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.397372911693886</v>
+        <v>-1.078319131124527</v>
       </c>
       <c r="U4" t="n">
-        <v>-14.06408604350547</v>
+        <v>-5.194465966907935</v>
       </c>
       <c r="V4" t="n">
-        <v>1.428581484321478</v>
+        <v>-5.982900496613697</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.616621156064735</v>
+        <v>4.761911790117157</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Bearish-neutral</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AA4" t="b">
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.5</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="b">
         <v>0</v>
@@ -1391,14 +1391,14 @@
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1426,73 +1426,73 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B5" t="n">
+        <v>4.329999923706055</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.394999980926514</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.179999828338623</v>
+      </c>
+      <c r="E5" t="n">
         <v>4.360000133514404</v>
       </c>
-      <c r="C5" t="n">
-        <v>4.53000020980835</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.300000190734863</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4.400000095367432</v>
-      </c>
       <c r="F5" t="n">
-        <v>24629000</v>
+        <v>26036000</v>
       </c>
       <c r="G5" t="n">
-        <v>4.396000003814697</v>
+        <v>4.42800006866455</v>
       </c>
       <c r="H5" t="n">
-        <v>4.507999992370605</v>
+        <v>4.509500002861023</v>
       </c>
       <c r="I5" t="n">
-        <v>5.024000000953674</v>
+        <v>5.01483333905538</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1449999888738</v>
+        <v>5.137416656812032</v>
       </c>
       <c r="K5" t="n">
-        <v>5.580249995986621</v>
+        <v>5.568166662255923</v>
       </c>
       <c r="L5" t="n">
-        <v>4.507999992370605</v>
+        <v>4.509500002861023</v>
       </c>
       <c r="M5" t="n">
-        <v>4.951602512826302</v>
+        <v>4.950764958446431</v>
       </c>
       <c r="N5" t="n">
-        <v>4.064397471914909</v>
+        <v>4.068235047275614</v>
       </c>
       <c r="O5" t="n">
-        <v>46.61431421053037</v>
+        <v>45.84221456274656</v>
       </c>
       <c r="P5" t="n">
-        <v>19.68067973409294</v>
+        <v>19.57046037500614</v>
       </c>
       <c r="Q5" t="n">
-        <v>23016805</v>
+        <v>23433515</v>
       </c>
       <c r="R5" t="n">
-        <v>1.070044256794112</v>
+        <v>1.11105824286284</v>
       </c>
       <c r="S5" t="n">
-        <v>3.286381665813742</v>
+        <v>-0.9090900224102638</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.078319131124527</v>
+        <v>-0.110219359086809</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.194465966907935</v>
+        <v>-0.5600383755845373</v>
       </c>
       <c r="V5" t="n">
-        <v>-5.982900496613697</v>
+        <v>-1.801800060249015</v>
       </c>
       <c r="W5" t="n">
-        <v>4.761911790117157</v>
+        <v>3.80953170274696</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
@@ -1512,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.66666666666667</v>
+        <v>20.83333333333334</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="b">
         <v>0</v>
@@ -1547,19 +1547,19 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Bearish trend bias</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AR5" t="b">
@@ -1576,79 +1576,79 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>Bearish trend bias</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B6" t="n">
-        <v>4.329999923706055</v>
+        <v>4.349999904632568</v>
       </c>
       <c r="C6" t="n">
-        <v>4.394999980926514</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="D6" t="n">
-        <v>4.179999828338623</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="E6" t="n">
-        <v>4.360000133514404</v>
+        <v>4.400000095367432</v>
       </c>
       <c r="F6" t="n">
-        <v>26036000</v>
+        <v>9422200</v>
       </c>
       <c r="G6" t="n">
-        <v>4.42800006866455</v>
+        <v>4.372000122070313</v>
       </c>
       <c r="H6" t="n">
-        <v>4.509500002861023</v>
+        <v>4.51100001335144</v>
       </c>
       <c r="I6" t="n">
-        <v>5.01483333905538</v>
+        <v>5.006833338737488</v>
       </c>
       <c r="J6" t="n">
-        <v>5.137416656812032</v>
+        <v>5.132999992370605</v>
       </c>
       <c r="K6" t="n">
-        <v>5.568166662255923</v>
+        <v>5.557833328843117</v>
       </c>
       <c r="L6" t="n">
-        <v>4.509500002861023</v>
+        <v>4.51100001335144</v>
       </c>
       <c r="M6" t="n">
-        <v>4.950764958446431</v>
+        <v>4.950468606628757</v>
       </c>
       <c r="N6" t="n">
-        <v>4.068235047275614</v>
+        <v>4.071531420074123</v>
       </c>
       <c r="O6" t="n">
-        <v>45.84221456274656</v>
+        <v>46.79133451906696</v>
       </c>
       <c r="P6" t="n">
-        <v>19.57046037500614</v>
+        <v>19.48430911002433</v>
       </c>
       <c r="Q6" t="n">
-        <v>23433515</v>
+        <v>23092330</v>
       </c>
       <c r="R6" t="n">
-        <v>1.11105824286284</v>
+        <v>0.4080229236287546</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9090900224102638</v>
+        <v>0.9174302896359121</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.110219359086809</v>
+        <v>-0.08615126498180103</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5600383755845373</v>
+        <v>-0.4402107223385854</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.801800060249015</v>
+        <v>3.286381665813742</v>
       </c>
       <c r="W6" t="n">
-        <v>3.80953170274696</v>
+        <v>-5.982900496613697</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
@@ -1668,18 +1668,18 @@
         <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.83333333333334</v>
+        <v>20</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Tight</t>
         </is>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
       <c r="AF6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Tight range with bearish bias</t>
         </is>
       </c>
       <c r="AR6" t="b">
@@ -1732,79 +1732,79 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Tight range with bearish bias</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B7" t="n">
-        <v>4.349999904632568</v>
+        <v>4.409999847412109</v>
       </c>
       <c r="C7" t="n">
-        <v>4.429999828338623</v>
+        <v>4.409999847412109</v>
       </c>
       <c r="D7" t="n">
-        <v>4.300000190734863</v>
+        <v>4.230000019073486</v>
       </c>
       <c r="E7" t="n">
-        <v>4.400000095367432</v>
+        <v>4.25</v>
       </c>
       <c r="F7" t="n">
-        <v>9422200</v>
+        <v>15948600</v>
       </c>
       <c r="G7" t="n">
-        <v>4.372000122070313</v>
+        <v>4.334000110626221</v>
       </c>
       <c r="H7" t="n">
-        <v>4.51100001335144</v>
+        <v>4.503000020980835</v>
       </c>
       <c r="I7" t="n">
-        <v>5.006833338737488</v>
+        <v>4.992666673660278</v>
       </c>
       <c r="J7" t="n">
-        <v>5.132999992370605</v>
+        <v>5.123749991257985</v>
       </c>
       <c r="K7" t="n">
-        <v>5.557833328843117</v>
+        <v>5.547458329796791</v>
       </c>
       <c r="L7" t="n">
-        <v>4.51100001335144</v>
+        <v>4.503000020980835</v>
       </c>
       <c r="M7" t="n">
-        <v>4.950468606628757</v>
+        <v>4.955832053778758</v>
       </c>
       <c r="N7" t="n">
-        <v>4.071531420074123</v>
+        <v>4.050167988182912</v>
       </c>
       <c r="O7" t="n">
-        <v>46.79133451906696</v>
+        <v>43.69858848893607</v>
       </c>
       <c r="P7" t="n">
-        <v>19.48430911002433</v>
+        <v>20.11245972409693</v>
       </c>
       <c r="Q7" t="n">
-        <v>23092330</v>
+        <v>23027100</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4080229236287546</v>
+        <v>0.6926013262634027</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9174302896359121</v>
+        <v>-3.409093002642438</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.08615126498180103</v>
+        <v>0.6281506140725988</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4402107223385854</v>
+        <v>3.223879330416834</v>
       </c>
       <c r="V7" t="n">
-        <v>3.286381665813742</v>
+        <v>-3.409093002642438</v>
       </c>
       <c r="W7" t="n">
-        <v>-5.982900496613697</v>
+        <v>-4.279280512879168</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
@@ -1814,28 +1814,28 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish-neutral</t>
         </is>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>20</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Tight</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
       <c r="AF7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="b">
         <v>0</v>
@@ -1859,19 +1859,19 @@
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO7" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Tight range with bearish bias</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
       <c r="AR7" t="b">
@@ -1888,79 +1888,79 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>Tight range with bearish bias</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B8" t="n">
-        <v>4.409999847412109</v>
+        <v>4.179999828338623</v>
       </c>
       <c r="C8" t="n">
-        <v>4.409999847412109</v>
+        <v>4.309999942779541</v>
       </c>
       <c r="D8" t="n">
-        <v>4.230000019073486</v>
+        <v>4.110000133514404</v>
       </c>
       <c r="E8" t="n">
-        <v>4.25</v>
+        <v>4.130000114440918</v>
       </c>
       <c r="F8" t="n">
-        <v>15948600</v>
+        <v>24567500</v>
       </c>
       <c r="G8" t="n">
-        <v>4.334000110626221</v>
+        <v>4.308000087738037</v>
       </c>
       <c r="H8" t="n">
-        <v>4.503000020980835</v>
+        <v>4.478000020980835</v>
       </c>
       <c r="I8" t="n">
-        <v>4.992666673660278</v>
+        <v>4.969500009218851</v>
       </c>
       <c r="J8" t="n">
-        <v>5.123749991257985</v>
+        <v>5.111583324273427</v>
       </c>
       <c r="K8" t="n">
-        <v>5.547458329796791</v>
+        <v>5.538333329558372</v>
       </c>
       <c r="L8" t="n">
-        <v>4.503000020980835</v>
+        <v>4.478000020980835</v>
       </c>
       <c r="M8" t="n">
-        <v>4.955832053778758</v>
+        <v>4.955828429666245</v>
       </c>
       <c r="N8" t="n">
-        <v>4.050167988182912</v>
+        <v>4.000171612295424</v>
       </c>
       <c r="O8" t="n">
-        <v>43.69858848893607</v>
+        <v>41.34425501634918</v>
       </c>
       <c r="P8" t="n">
-        <v>20.11245972409693</v>
+        <v>21.34115258805871</v>
       </c>
       <c r="Q8" t="n">
-        <v>23027100</v>
+        <v>23726935</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6926013262634027</v>
+        <v>1.03542661536351</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.409093002642438</v>
+        <v>-2.823526719037228</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6281506140725988</v>
+        <v>1.228692863961779</v>
       </c>
       <c r="U8" t="n">
-        <v>3.223879330416834</v>
+        <v>6.109112862459432</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.409093002642438</v>
+        <v>-5.275229633722356</v>
       </c>
       <c r="W8" t="n">
-        <v>-4.279280512879168</v>
+        <v>-3.051645714935569</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="AA8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="b">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.66666666666667</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2015,19 +2015,19 @@
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Bearish trend bias</t>
+          <t>Expansion with bearish bias</t>
         </is>
       </c>
       <c r="AR8" t="b">
@@ -2044,79 +2044,79 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>Bearish trend bias</t>
+          <t>Expansion with bearish bias</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B9" t="n">
-        <v>4.179999828338623</v>
+        <v>4.150000095367432</v>
       </c>
       <c r="C9" t="n">
-        <v>4.309999942779541</v>
+        <v>4.210000038146973</v>
       </c>
       <c r="D9" t="n">
+        <v>4.099999904632568</v>
+      </c>
+      <c r="E9" t="n">
         <v>4.110000133514404</v>
       </c>
-      <c r="E9" t="n">
-        <v>4.130000114440918</v>
-      </c>
       <c r="F9" t="n">
-        <v>24567500</v>
+        <v>18023800</v>
       </c>
       <c r="G9" t="n">
-        <v>4.308000087738037</v>
+        <v>4.250000095367431</v>
       </c>
       <c r="H9" t="n">
-        <v>4.478000020980835</v>
+        <v>4.465500020980835</v>
       </c>
       <c r="I9" t="n">
-        <v>4.969500009218851</v>
+        <v>4.946500015258789</v>
       </c>
       <c r="J9" t="n">
-        <v>5.111583324273427</v>
+        <v>5.098208324114482</v>
       </c>
       <c r="K9" t="n">
-        <v>5.538333329558372</v>
+        <v>5.528708329796791</v>
       </c>
       <c r="L9" t="n">
-        <v>4.478000020980835</v>
+        <v>4.465500020980835</v>
       </c>
       <c r="M9" t="n">
-        <v>4.955828429666245</v>
+        <v>4.968730613187603</v>
       </c>
       <c r="N9" t="n">
-        <v>4.000171612295424</v>
+        <v>3.962269428774068</v>
       </c>
       <c r="O9" t="n">
-        <v>41.34425501634918</v>
+        <v>40.94827830223937</v>
       </c>
       <c r="P9" t="n">
-        <v>21.34115258805871</v>
+        <v>22.53859992575856</v>
       </c>
       <c r="Q9" t="n">
-        <v>23726935</v>
+        <v>23715255</v>
       </c>
       <c r="R9" t="n">
-        <v>1.03542661536351</v>
+        <v>0.760008694825335</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.823526719037228</v>
+        <v>-0.4842610259641833</v>
       </c>
       <c r="T9" t="n">
-        <v>1.228692863961779</v>
+        <v>1.197447337699845</v>
       </c>
       <c r="U9" t="n">
-        <v>6.109112862459432</v>
+        <v>5.610977817429919</v>
       </c>
       <c r="V9" t="n">
-        <v>-5.275229633722356</v>
+        <v>-6.59090808107835</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.051645714935569</v>
+        <v>-6.59090808107835</v>
       </c>
       <c r="X9" t="b">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="b">
         <v>0</v>
@@ -2206,73 +2206,73 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B10" t="n">
-        <v>4.150000095367432</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="C10" t="n">
-        <v>4.210000038146973</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="D10" t="n">
-        <v>4.099999904632568</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="E10" t="n">
-        <v>4.110000133514404</v>
+        <v>4.090000152587891</v>
       </c>
       <c r="F10" t="n">
-        <v>18023800</v>
+        <v>15217400</v>
       </c>
       <c r="G10" t="n">
-        <v>4.250000095367431</v>
+        <v>4.196000099182129</v>
       </c>
       <c r="H10" t="n">
-        <v>4.465500020980835</v>
+        <v>4.454000020027161</v>
       </c>
       <c r="I10" t="n">
-        <v>4.946500015258789</v>
+        <v>4.922500014305115</v>
       </c>
       <c r="J10" t="n">
-        <v>5.098208324114482</v>
+        <v>5.088291656970978</v>
       </c>
       <c r="K10" t="n">
-        <v>5.528708329796791</v>
+        <v>5.51908333003521</v>
       </c>
       <c r="L10" t="n">
-        <v>4.465500020980835</v>
+        <v>4.454000020027161</v>
       </c>
       <c r="M10" t="n">
-        <v>4.968730613187603</v>
+        <v>4.981173182830053</v>
       </c>
       <c r="N10" t="n">
-        <v>3.962269428774068</v>
+        <v>3.926826857224269</v>
       </c>
       <c r="O10" t="n">
-        <v>40.94827830223937</v>
+        <v>40.53023784660396</v>
       </c>
       <c r="P10" t="n">
-        <v>22.53859992575856</v>
+        <v>23.67189763953695</v>
       </c>
       <c r="Q10" t="n">
-        <v>23715255</v>
+        <v>23595080</v>
       </c>
       <c r="R10" t="n">
-        <v>0.760008694825335</v>
+        <v>0.6449395382427184</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4842610259641833</v>
+        <v>-0.4866175249831906</v>
       </c>
       <c r="T10" t="n">
-        <v>1.197447337699845</v>
+        <v>1.13329771377839</v>
       </c>
       <c r="U10" t="n">
-        <v>5.610977817429919</v>
+        <v>5.028252497987618</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.59090808107835</v>
+        <v>-3.764702292049638</v>
       </c>
       <c r="W10" t="n">
-        <v>-6.59090808107835</v>
+        <v>-6.192659923358268</v>
       </c>
       <c r="X10" t="b">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>23.33333333333333</v>
+        <v>25</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO10" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2362,73 +2362,73 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B11" t="n">
-        <v>4.099999904632568</v>
+        <v>4.170000076293945</v>
       </c>
       <c r="C11" t="n">
-        <v>4.139999866485596</v>
+        <v>4.230000019073486</v>
       </c>
       <c r="D11" t="n">
-        <v>4.050000190734863</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="E11" t="n">
-        <v>4.090000152587891</v>
+        <v>4.199999809265137</v>
       </c>
       <c r="F11" t="n">
-        <v>15217400</v>
+        <v>16227200</v>
       </c>
       <c r="G11" t="n">
-        <v>4.196000099182129</v>
+        <v>4.15600004196167</v>
       </c>
       <c r="H11" t="n">
-        <v>4.454000020027161</v>
+        <v>4.431000018119812</v>
       </c>
       <c r="I11" t="n">
-        <v>4.922500014305115</v>
+        <v>4.905333344141642</v>
       </c>
       <c r="J11" t="n">
-        <v>5.088291656970978</v>
+        <v>5.079291653633118</v>
       </c>
       <c r="K11" t="n">
-        <v>5.51908333003521</v>
+        <v>5.509374995032946</v>
       </c>
       <c r="L11" t="n">
-        <v>4.454000020027161</v>
+        <v>4.431000018119812</v>
       </c>
       <c r="M11" t="n">
-        <v>4.981173182830053</v>
+        <v>4.960464496016389</v>
       </c>
       <c r="N11" t="n">
-        <v>3.926826857224269</v>
+        <v>3.901535540223236</v>
       </c>
       <c r="O11" t="n">
-        <v>40.53023784660396</v>
+        <v>43.92123583393309</v>
       </c>
       <c r="P11" t="n">
-        <v>23.67189763953695</v>
+        <v>23.89819344307933</v>
       </c>
       <c r="Q11" t="n">
-        <v>23595080</v>
+        <v>23415325</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6449395382427184</v>
+        <v>0.6930162190787443</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4866175249831906</v>
+        <v>2.689478058030037</v>
       </c>
       <c r="T11" t="n">
-        <v>1.13329771377839</v>
+        <v>0.2262958035423814</v>
       </c>
       <c r="U11" t="n">
-        <v>5.028252497987618</v>
+        <v>0.9559681567920419</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.764702292049638</v>
+        <v>1.694907818027858</v>
       </c>
       <c r="W11" t="n">
-        <v>-6.192659923358268</v>
+        <v>-4.545460949259217</v>
       </c>
       <c r="X11" t="b">
         <v>0</v>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="b">
         <v>0</v>
@@ -2518,73 +2518,73 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B12" t="n">
-        <v>4.170000076293945</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="C12" t="n">
-        <v>4.230000019073486</v>
+        <v>4.420000076293945</v>
       </c>
       <c r="D12" t="n">
-        <v>4.119999885559082</v>
+        <v>4.25</v>
       </c>
       <c r="E12" t="n">
-        <v>4.199999809265137</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="F12" t="n">
-        <v>16227200</v>
+        <v>17617900</v>
       </c>
       <c r="G12" t="n">
-        <v>4.15600004196167</v>
+        <v>4.180000019073487</v>
       </c>
       <c r="H12" t="n">
-        <v>4.431000018119812</v>
+        <v>4.403500008583069</v>
       </c>
       <c r="I12" t="n">
-        <v>4.905333344141642</v>
+        <v>4.876666673024496</v>
       </c>
       <c r="J12" t="n">
-        <v>5.079291653633118</v>
+        <v>5.072208321094513</v>
       </c>
       <c r="K12" t="n">
-        <v>5.509374995032946</v>
+        <v>5.498916660745938</v>
       </c>
       <c r="L12" t="n">
-        <v>4.431000018119812</v>
+        <v>4.403500008583069</v>
       </c>
       <c r="M12" t="n">
-        <v>4.960464496016389</v>
+        <v>4.880564487778075</v>
       </c>
       <c r="N12" t="n">
-        <v>3.901535540223236</v>
+        <v>3.926435529388063</v>
       </c>
       <c r="O12" t="n">
-        <v>43.92123583393309</v>
+        <v>48.78191685005874</v>
       </c>
       <c r="P12" t="n">
-        <v>23.89819344307933</v>
+        <v>21.6675134899574</v>
       </c>
       <c r="Q12" t="n">
-        <v>23415325</v>
+        <v>23300940</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6930162190787443</v>
+        <v>0.7561025435025368</v>
       </c>
       <c r="S12" t="n">
-        <v>2.689478058030037</v>
+        <v>4.047621047956418</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2262958035423814</v>
+        <v>-2.230679953121928</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9559681567920419</v>
+        <v>-9.33409447218242</v>
       </c>
       <c r="V12" t="n">
-        <v>1.694907818027858</v>
+        <v>6.326027824781488</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.545460949259217</v>
+        <v>2.823526719037228</v>
       </c>
       <c r="X12" t="b">
         <v>0</v>
@@ -2594,17 +2594,17 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Bearish-neutral</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="b">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>25</v>
+        <v>20.83333333333334</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2636,22 +2636,22 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Expansion with bearish bias</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AR12" t="b">
@@ -2668,110 +2668,110 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>Expansion with bearish bias</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B13" t="n">
-        <v>4.260000228881836</v>
+        <v>4.360000133514404</v>
       </c>
       <c r="C13" t="n">
-        <v>4.420000076293945</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="D13" t="n">
-        <v>4.25</v>
+        <v>4.349999904632568</v>
       </c>
       <c r="E13" t="n">
-        <v>4.369999885559082</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="F13" t="n">
-        <v>17617900</v>
+        <v>23178000</v>
       </c>
       <c r="G13" t="n">
-        <v>4.180000019073487</v>
+        <v>4.264000034332275</v>
       </c>
       <c r="H13" t="n">
-        <v>4.403500008583069</v>
+        <v>4.395500016212464</v>
       </c>
       <c r="I13" t="n">
-        <v>4.876666673024496</v>
+        <v>4.854000012079875</v>
       </c>
       <c r="J13" t="n">
-        <v>5.072208321094513</v>
+        <v>5.065208323796591</v>
       </c>
       <c r="K13" t="n">
-        <v>5.498916660745938</v>
+        <v>5.486666662494342</v>
       </c>
       <c r="L13" t="n">
-        <v>4.403500008583069</v>
+        <v>4.395500016212464</v>
       </c>
       <c r="M13" t="n">
-        <v>4.880564487778075</v>
+        <v>4.856002029445357</v>
       </c>
       <c r="N13" t="n">
-        <v>3.926435529388063</v>
+        <v>3.93499800297957</v>
       </c>
       <c r="O13" t="n">
-        <v>48.78191685005874</v>
+        <v>53.38870908853723</v>
       </c>
       <c r="P13" t="n">
-        <v>21.6675134899574</v>
+        <v>20.95333916661894</v>
       </c>
       <c r="Q13" t="n">
-        <v>23300940</v>
+        <v>23603435</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7561025435025368</v>
+        <v>0.9819757166700525</v>
       </c>
       <c r="S13" t="n">
-        <v>4.047621047956418</v>
+        <v>4.119000226306713</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.230679953121928</v>
+        <v>-0.7141743233384652</v>
       </c>
       <c r="U13" t="n">
-        <v>-9.33409447218242</v>
+        <v>-3.296060360915321</v>
       </c>
       <c r="V13" t="n">
-        <v>6.326027824781488</v>
+        <v>11.24694427837403</v>
       </c>
       <c r="W13" t="n">
-        <v>2.823526719037228</v>
+        <v>10.16949309094151</v>
       </c>
       <c r="X13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="b">
         <v>0</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bullish-neutral</t>
         </is>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
       </c>
       <c r="AB13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.83333333333334</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Tight</t>
         </is>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
       <c r="AF13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
@@ -2792,14 +2792,14 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
         <v>2</v>
       </c>
-      <c r="AO13" t="n">
-        <v>-1</v>
-      </c>
       <c r="AP13" t="inlineStr">
         <is>
           <t>Weak</t>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Tight range with bullish bias</t>
         </is>
       </c>
       <c r="AR13" t="b">
@@ -2824,96 +2824,96 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Tight range with bullish bias</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B14" t="n">
-        <v>4.360000133514404</v>
+        <v>4.554999828338623</v>
       </c>
       <c r="C14" t="n">
-        <v>4.659999847412109</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4.349999904632568</v>
+        <v>4.544000148773193</v>
       </c>
       <c r="E14" t="n">
-        <v>4.550000190734863</v>
+        <v>4.860000133514404</v>
       </c>
       <c r="F14" t="n">
-        <v>23178000</v>
+        <v>33116700</v>
       </c>
       <c r="G14" t="n">
-        <v>4.264000034332275</v>
+        <v>4.414000034332275</v>
       </c>
       <c r="H14" t="n">
-        <v>4.395500016212464</v>
+        <v>4.397500014305114</v>
       </c>
       <c r="I14" t="n">
-        <v>4.854000012079875</v>
+        <v>4.846333344777425</v>
       </c>
       <c r="J14" t="n">
-        <v>5.065208323796591</v>
+        <v>5.059708325068156</v>
       </c>
       <c r="K14" t="n">
-        <v>5.486666662494342</v>
+        <v>5.47554166217645</v>
       </c>
       <c r="L14" t="n">
-        <v>4.395500016212464</v>
+        <v>4.397500014305114</v>
       </c>
       <c r="M14" t="n">
-        <v>4.856002029445357</v>
+        <v>4.866041979410933</v>
       </c>
       <c r="N14" t="n">
-        <v>3.93499800297957</v>
+        <v>3.928958049199295</v>
       </c>
       <c r="O14" t="n">
-        <v>53.38870908853723</v>
+        <v>60.05271836140502</v>
       </c>
       <c r="P14" t="n">
-        <v>20.95333916661894</v>
+        <v>21.30946963418519</v>
       </c>
       <c r="Q14" t="n">
-        <v>23603435</v>
+        <v>23512290</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9819757166700525</v>
+        <v>1.408484669081574</v>
       </c>
       <c r="S14" t="n">
-        <v>4.119000226306713</v>
+        <v>6.813185269987287</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7141743233384652</v>
+        <v>0.3561304675662562</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.296060360915321</v>
+        <v>1.699635865836657</v>
       </c>
       <c r="V14" t="n">
-        <v>11.24694427837403</v>
+        <v>15.71429414814061</v>
       </c>
       <c r="W14" t="n">
-        <v>10.16949309094151</v>
+        <v>18.24817458968513</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Bullish-neutral</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>19.16666666666667</v>
@@ -2948,17 +2948,17 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -2986,83 +2986,83 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B15" t="n">
-        <v>4.554999828338623</v>
+        <v>4.795000076293945</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>4.795000076293945</v>
       </c>
       <c r="D15" t="n">
-        <v>4.544000148773193</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="E15" t="n">
-        <v>4.860000133514404</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="F15" t="n">
-        <v>33116700</v>
+        <v>17187200</v>
       </c>
       <c r="G15" t="n">
-        <v>4.414000034332275</v>
+        <v>4.535999965667725</v>
       </c>
       <c r="H15" t="n">
-        <v>4.397500014305114</v>
+        <v>4.394000005722046</v>
       </c>
       <c r="I15" t="n">
-        <v>4.846333344777425</v>
+        <v>4.832500004768372</v>
       </c>
       <c r="J15" t="n">
-        <v>5.059708325068156</v>
+        <v>5.050208322207133</v>
       </c>
       <c r="K15" t="n">
-        <v>5.47554166217645</v>
+        <v>5.464583328366279</v>
       </c>
       <c r="L15" t="n">
-        <v>4.397500014305114</v>
+        <v>4.394000005722046</v>
       </c>
       <c r="M15" t="n">
-        <v>4.866041979410933</v>
+        <v>4.851747320911755</v>
       </c>
       <c r="N15" t="n">
-        <v>3.928958049199295</v>
+        <v>3.936252690532337</v>
       </c>
       <c r="O15" t="n">
-        <v>60.05271836140502</v>
+        <v>55.63180932535478</v>
       </c>
       <c r="P15" t="n">
-        <v>21.30946963418519</v>
+        <v>20.83510762829368</v>
       </c>
       <c r="Q15" t="n">
-        <v>23512290</v>
+        <v>23484485</v>
       </c>
       <c r="R15" t="n">
-        <v>1.408484669081574</v>
+        <v>0.7318533917179789</v>
       </c>
       <c r="S15" t="n">
-        <v>6.813185269987287</v>
+        <v>-3.292187651311174</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3561304675662562</v>
+        <v>-0.4743620058915141</v>
       </c>
       <c r="U15" t="n">
-        <v>1.699635865836657</v>
+        <v>-2.226061999828144</v>
       </c>
       <c r="V15" t="n">
-        <v>15.71429414814061</v>
+        <v>7.551485866087981</v>
       </c>
       <c r="W15" t="n">
-        <v>18.24817458968513</v>
+        <v>14.91441647725311</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
       <c r="Y15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bullish-neutral</t>
         </is>
       </c>
       <c r="AA15" t="b">
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.16666666666667</v>
+        <v>17.5</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -3092,10 +3092,10 @@
         <v>0</v>
       </c>
       <c r="AI15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="b">
         <v>0</v>
@@ -3104,17 +3104,17 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3142,73 +3142,73 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B16" t="n">
-        <v>4.795000076293945</v>
+        <v>4.78000020980835</v>
       </c>
       <c r="C16" t="n">
-        <v>4.795000076293945</v>
+        <v>4.815000057220459</v>
       </c>
       <c r="D16" t="n">
-        <v>4.650000095367432</v>
+        <v>4.619999885559082</v>
       </c>
       <c r="E16" t="n">
-        <v>4.699999809265137</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="F16" t="n">
-        <v>17187200</v>
+        <v>15381300</v>
       </c>
       <c r="G16" t="n">
-        <v>4.535999965667725</v>
+        <v>4.627999973297119</v>
       </c>
       <c r="H16" t="n">
-        <v>4.394000005722046</v>
+        <v>4.388499999046326</v>
       </c>
       <c r="I16" t="n">
-        <v>4.832500004768372</v>
+        <v>4.81200000445048</v>
       </c>
       <c r="J16" t="n">
-        <v>5.050208322207133</v>
+        <v>5.035708320140839</v>
       </c>
       <c r="K16" t="n">
-        <v>5.464583328366279</v>
+        <v>5.454708326856295</v>
       </c>
       <c r="L16" t="n">
-        <v>4.394000005722046</v>
+        <v>4.388499999046326</v>
       </c>
       <c r="M16" t="n">
-        <v>4.851747320911755</v>
+        <v>4.829564454207822</v>
       </c>
       <c r="N16" t="n">
-        <v>3.936252690532337</v>
+        <v>3.94743554388483</v>
       </c>
       <c r="O16" t="n">
-        <v>55.63180932535478</v>
+        <v>54.55061939598142</v>
       </c>
       <c r="P16" t="n">
-        <v>20.83510762829368</v>
+        <v>20.10092082749663</v>
       </c>
       <c r="Q16" t="n">
-        <v>23484485</v>
+        <v>23569370</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7318533917179789</v>
+        <v>0.6525969934707632</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.292187651311174</v>
+        <v>-0.851063052687262</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4743620058915141</v>
+        <v>-0.7341868007970476</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.226061999828144</v>
+        <v>-3.523796535612977</v>
       </c>
       <c r="V16" t="n">
-        <v>7.551485866087981</v>
+        <v>2.417574770683251</v>
       </c>
       <c r="W16" t="n">
-        <v>14.91441647725311</v>
+        <v>10.95238235802343</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
@@ -3225,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.5</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="b">
         <v>0</v>
@@ -3260,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN16" t="n">
         <v>1</v>
       </c>
       <c r="AO16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Tight range with bullish bias</t>
+          <t>Tight range</t>
         </is>
       </c>
       <c r="AR16" t="b">
@@ -3292,85 +3292,85 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>Tight range with bullish bias</t>
+          <t>Tight range</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B17" t="n">
-        <v>4.78000020980835</v>
+        <v>4.760000228881836</v>
       </c>
       <c r="C17" t="n">
-        <v>4.815000057220459</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="D17" t="n">
-        <v>4.619999885559082</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="E17" t="n">
-        <v>4.659999847412109</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="F17" t="n">
-        <v>15381300</v>
+        <v>24699500</v>
       </c>
       <c r="G17" t="n">
-        <v>4.627999973297119</v>
+        <v>4.715999984741211</v>
       </c>
       <c r="H17" t="n">
-        <v>4.388499999046326</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>4.81200000445048</v>
+        <v>4.779000004132588</v>
       </c>
       <c r="J17" t="n">
-        <v>5.035708320140839</v>
+        <v>5.021291653315227</v>
       </c>
       <c r="K17" t="n">
-        <v>5.454708326856295</v>
+        <v>5.443791660666466</v>
       </c>
       <c r="L17" t="n">
-        <v>4.388499999046326</v>
+        <v>4.4</v>
       </c>
       <c r="M17" t="n">
-        <v>4.829564454207822</v>
+        <v>4.872930346627679</v>
       </c>
       <c r="N17" t="n">
-        <v>3.94743554388483</v>
+        <v>3.927069653372322</v>
       </c>
       <c r="O17" t="n">
-        <v>54.55061939598142</v>
+        <v>57.85818653729903</v>
       </c>
       <c r="P17" t="n">
-        <v>20.10092082749663</v>
+        <v>21.49683393762175</v>
       </c>
       <c r="Q17" t="n">
-        <v>23569370</v>
+        <v>24125555</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525969934707632</v>
+        <v>1.023789919029842</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.851063052687262</v>
+        <v>3.218886272082888</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7341868007970476</v>
+        <v>1.395913110125125</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.523796535612977</v>
+        <v>6.944523199233821</v>
       </c>
       <c r="V17" t="n">
-        <v>2.417574770683251</v>
+        <v>-1.028810480684217</v>
       </c>
       <c r="W17" t="n">
-        <v>10.95238235802343</v>
+        <v>10.06865145865254</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -3381,21 +3381,21 @@
         <v>0</v>
       </c>
       <c r="AB17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.16666666666667</v>
+        <v>20.83333333333334</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Tight</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
       <c r="AF17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="b">
         <v>0</v>
@@ -3416,22 +3416,22 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Tight range</t>
+          <t>Bullish trend bias</t>
         </is>
       </c>
       <c r="AR17" t="b">
@@ -3448,85 +3448,85 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>Tight range</t>
+          <t>Bullish trend bias</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B18" t="n">
-        <v>4.760000228881836</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="C18" t="n">
-        <v>4.980000019073486</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="D18" t="n">
-        <v>4.71999979019165</v>
+        <v>4.630000114440918</v>
       </c>
       <c r="E18" t="n">
-        <v>4.809999942779541</v>
+        <v>4.690000057220459</v>
       </c>
       <c r="F18" t="n">
-        <v>24699500</v>
+        <v>18996400</v>
       </c>
       <c r="G18" t="n">
-        <v>4.715999984741211</v>
+        <v>4.74399995803833</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.418000006675721</v>
       </c>
       <c r="I18" t="n">
-        <v>4.779000004132588</v>
+        <v>4.75116666952769</v>
       </c>
       <c r="J18" t="n">
-        <v>5.021291653315227</v>
+        <v>5.006791655222575</v>
       </c>
       <c r="K18" t="n">
-        <v>5.443791660666466</v>
+        <v>5.433499994874</v>
       </c>
       <c r="L18" t="n">
-        <v>4.4</v>
+        <v>4.418000006675721</v>
       </c>
       <c r="M18" t="n">
-        <v>4.872930346627679</v>
+        <v>4.906848234832417</v>
       </c>
       <c r="N18" t="n">
-        <v>3.927069653372322</v>
+        <v>3.929151778519024</v>
       </c>
       <c r="O18" t="n">
-        <v>57.85818653729903</v>
+        <v>54.44461054459855</v>
       </c>
       <c r="P18" t="n">
-        <v>21.49683393762175</v>
+        <v>22.12984279846234</v>
       </c>
       <c r="Q18" t="n">
-        <v>24125555</v>
+        <v>24176460</v>
       </c>
       <c r="R18" t="n">
-        <v>1.023789919029842</v>
+        <v>0.7857395168688882</v>
       </c>
       <c r="S18" t="n">
-        <v>3.218886272082888</v>
+        <v>-2.494800145251941</v>
       </c>
       <c r="T18" t="n">
-        <v>1.395913110125125</v>
+        <v>0.6330088608405866</v>
       </c>
       <c r="U18" t="n">
-        <v>6.944523199233821</v>
+        <v>2.944660886702732</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.028810480684217</v>
+        <v>-0.212760690435887</v>
       </c>
       <c r="W18" t="n">
-        <v>10.06865145865254</v>
+        <v>3.076920013556839</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
       <c r="Y18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="AA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="b">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.83333333333334</v>
+        <v>22.5</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AI18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="b">
         <v>0</v>
@@ -3572,22 +3572,22 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Bullish trend bias</t>
+          <t>Expansion without full confirmation</t>
         </is>
       </c>
       <c r="AR18" t="b">
@@ -3604,85 +3604,85 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>Bullish trend bias</t>
+          <t>Expansion without full confirmation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B19" t="n">
-        <v>4.880000114440918</v>
+        <v>4.619999885559082</v>
       </c>
       <c r="C19" t="n">
-        <v>4.960000038146973</v>
+        <v>4.869999885559082</v>
       </c>
       <c r="D19" t="n">
-        <v>4.630000114440918</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="E19" t="n">
-        <v>4.690000057220459</v>
+        <v>4.849999904632568</v>
       </c>
       <c r="F19" t="n">
-        <v>18996400</v>
+        <v>16954800</v>
       </c>
       <c r="G19" t="n">
-        <v>4.74399995803833</v>
+        <v>4.741999912261963</v>
       </c>
       <c r="H19" t="n">
-        <v>4.418000006675721</v>
+        <v>4.450500011444092</v>
       </c>
       <c r="I19" t="n">
-        <v>4.75116666952769</v>
+        <v>4.734333332379659</v>
       </c>
       <c r="J19" t="n">
-        <v>5.006791655222575</v>
+        <v>4.995041652520498</v>
       </c>
       <c r="K19" t="n">
-        <v>5.433499994874</v>
+        <v>5.421666660904885</v>
       </c>
       <c r="L19" t="n">
-        <v>4.418000006675721</v>
+        <v>4.450500011444092</v>
       </c>
       <c r="M19" t="n">
-        <v>4.906848234832417</v>
+        <v>4.964123798170175</v>
       </c>
       <c r="N19" t="n">
-        <v>3.929151778519024</v>
+        <v>3.936876224718008</v>
       </c>
       <c r="O19" t="n">
-        <v>54.44461054459855</v>
+        <v>58.00249370590777</v>
       </c>
       <c r="P19" t="n">
-        <v>22.12984279846234</v>
+        <v>23.08162163376441</v>
       </c>
       <c r="Q19" t="n">
-        <v>24176460</v>
+        <v>24153445</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7857395168688882</v>
+        <v>0.7019619768525773</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.494800145251941</v>
+        <v>3.411510564179698</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6330088608405866</v>
+        <v>0.951778835302072</v>
       </c>
       <c r="U19" t="n">
-        <v>2.944660886702732</v>
+        <v>4.300883851593396</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.212760690435887</v>
+        <v>4.077254580297329</v>
       </c>
       <c r="W19" t="n">
-        <v>3.076920013556839</v>
+        <v>-0.2057660207223977</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>22.5</v>
+        <v>25.83333333333334</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3716,10 +3716,10 @@
         <v>0</v>
       </c>
       <c r="AI19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="b">
         <v>0</v>
@@ -3728,22 +3728,22 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Expansion without full confirmation</t>
+          <t>Expansion with bullish bias</t>
         </is>
       </c>
       <c r="AR19" t="b">
@@ -3760,85 +3760,85 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>Expansion without full confirmation</t>
+          <t>Expansion with bullish bias</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B20" t="n">
-        <v>4.619999885559082</v>
+        <v>4.849999904632568</v>
       </c>
       <c r="C20" t="n">
         <v>4.869999885559082</v>
       </c>
       <c r="D20" t="n">
-        <v>4.610000133514404</v>
+        <v>4.630000114440918</v>
       </c>
       <c r="E20" t="n">
-        <v>4.849999904632568</v>
+        <v>4.639999866485596</v>
       </c>
       <c r="F20" t="n">
-        <v>16954800</v>
+        <v>19182700</v>
       </c>
       <c r="G20" t="n">
-        <v>4.741999912261963</v>
+        <v>4.729999923706055</v>
       </c>
       <c r="H20" t="n">
-        <v>4.450500011444092</v>
+        <v>4.472500014305115</v>
       </c>
       <c r="I20" t="n">
-        <v>4.734333332379659</v>
+        <v>4.700333333015442</v>
       </c>
       <c r="J20" t="n">
-        <v>4.995041652520498</v>
+        <v>4.97962498664856</v>
       </c>
       <c r="K20" t="n">
-        <v>5.421666660904885</v>
+        <v>5.410833327968915</v>
       </c>
       <c r="L20" t="n">
-        <v>4.450500011444092</v>
+        <v>4.472500014305115</v>
       </c>
       <c r="M20" t="n">
-        <v>4.964123798170175</v>
+        <v>4.978583939971046</v>
       </c>
       <c r="N20" t="n">
-        <v>3.936876224718008</v>
+        <v>3.966416088639183</v>
       </c>
       <c r="O20" t="n">
-        <v>58.00249370590777</v>
+        <v>52.23606579607813</v>
       </c>
       <c r="P20" t="n">
-        <v>23.08162163376441</v>
+        <v>22.63091890652844</v>
       </c>
       <c r="Q20" t="n">
-        <v>24153445</v>
+        <v>24431720</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7019619768525773</v>
+        <v>0.7851555273226772</v>
       </c>
       <c r="S20" t="n">
-        <v>3.411510564179698</v>
+        <v>-4.329897778892478</v>
       </c>
       <c r="T20" t="n">
-        <v>0.951778835302072</v>
+        <v>-0.4507027272359707</v>
       </c>
       <c r="U20" t="n">
-        <v>4.300883851593396</v>
+        <v>-1.952647584243694</v>
       </c>
       <c r="V20" t="n">
-        <v>4.077254580297329</v>
+        <v>-3.53430516250085</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.2057660207223977</v>
+        <v>-1.276594579030887</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
       <c r="Y20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -3846,13 +3846,13 @@
         </is>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="b">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>25.83333333333334</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3872,10 +3872,10 @@
         <v>0</v>
       </c>
       <c r="AI20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="b">
         <v>0</v>
@@ -3884,22 +3884,22 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Expansion with bullish bias</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AR20" t="b">
@@ -3916,79 +3916,79 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>Expansion with bullish bias</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B21" t="n">
-        <v>4.849999904632568</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="C21" t="n">
-        <v>4.869999885559082</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="D21" t="n">
-        <v>4.630000114440918</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="E21" t="n">
-        <v>4.639999866485596</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="F21" t="n">
-        <v>19182700</v>
+        <v>21430700</v>
       </c>
       <c r="G21" t="n">
-        <v>4.729999923706055</v>
+        <v>4.731999969482422</v>
       </c>
       <c r="H21" t="n">
-        <v>4.472500014305115</v>
+        <v>4.472000026702881</v>
       </c>
       <c r="I21" t="n">
-        <v>4.700333333015442</v>
+        <v>4.676333332061768</v>
       </c>
       <c r="J21" t="n">
-        <v>4.97962498664856</v>
+        <v>4.965958321094513</v>
       </c>
       <c r="K21" t="n">
-        <v>5.410833327968915</v>
+        <v>5.400083328286807</v>
       </c>
       <c r="L21" t="n">
-        <v>4.472500014305115</v>
+        <v>4.472000026702881</v>
       </c>
       <c r="M21" t="n">
-        <v>4.978583939971046</v>
+        <v>4.977239848036836</v>
       </c>
       <c r="N21" t="n">
-        <v>3.966416088639183</v>
+        <v>3.966760205368926</v>
       </c>
       <c r="O21" t="n">
-        <v>52.23606579607813</v>
+        <v>52.9556102701212</v>
       </c>
       <c r="P21" t="n">
-        <v>22.63091890652844</v>
+        <v>22.59569849360931</v>
       </c>
       <c r="Q21" t="n">
-        <v>24431720</v>
+        <v>22225515</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7851555273226772</v>
+        <v>0.9642386239418974</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.329897778892478</v>
+        <v>0.6465562644740297</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4507027272359707</v>
+        <v>-0.0352204129191378</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.952647584243694</v>
+        <v>-0.1556296192152251</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.53430516250085</v>
+        <v>-0.4264388205224567</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.276594579030887</v>
+        <v>0.2145971933322999</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="AB21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
         <v>24.16666666666667</v>
@@ -4031,7 +4031,7 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="b">
         <v>0</v>
@@ -4078,93 +4078,93 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B22" t="n">
-        <v>4.650000095367432</v>
+        <v>4.460000038146973</v>
       </c>
       <c r="C22" t="n">
-        <v>4.880000114440918</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="D22" t="n">
-        <v>4.550000190734863</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="E22" t="n">
-        <v>4.670000076293945</v>
+        <v>4.400000095367432</v>
       </c>
       <c r="F22" t="n">
-        <v>21430700</v>
+        <v>22287800</v>
       </c>
       <c r="G22" t="n">
-        <v>4.731999969482422</v>
+        <v>4.65</v>
       </c>
       <c r="H22" t="n">
-        <v>4.472000026702881</v>
+        <v>4.470000028610229</v>
       </c>
       <c r="I22" t="n">
-        <v>4.676333332061768</v>
+        <v>4.653833333651225</v>
       </c>
       <c r="J22" t="n">
-        <v>4.965958321094513</v>
+        <v>4.953041656812032</v>
       </c>
       <c r="K22" t="n">
-        <v>5.400083328286807</v>
+        <v>5.386708328127861</v>
       </c>
       <c r="L22" t="n">
-        <v>4.472000026702881</v>
+        <v>4.470000028610229</v>
       </c>
       <c r="M22" t="n">
-        <v>4.977239848036836</v>
+        <v>4.976089173713814</v>
       </c>
       <c r="N22" t="n">
-        <v>3.966760205368926</v>
+        <v>3.963910883506645</v>
       </c>
       <c r="O22" t="n">
-        <v>52.9556102701212</v>
+        <v>46.2086933314685</v>
       </c>
       <c r="P22" t="n">
-        <v>22.59569849360931</v>
+        <v>22.64380947938978</v>
       </c>
       <c r="Q22" t="n">
-        <v>22225515</v>
+        <v>21755665</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9642386239418974</v>
+        <v>1.024459606268069</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6465562644740297</v>
+        <v>-5.781584079561353</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0352204129191378</v>
+        <v>0.04811098578047535</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1556296192152251</v>
+        <v>0.2129209937638432</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.4264388205224567</v>
+        <v>-9.278346765230062</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2145971933322999</v>
+        <v>-8.523905453004721</v>
       </c>
       <c r="X22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="b">
         <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Bullish-neutral</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>24.16666666666667</v>
+        <v>25.83333333333334</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="b">
         <v>0</v>
@@ -4196,22 +4196,22 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO22" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
       <c r="AR22" t="b">
@@ -4228,148 +4228,148 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B23" t="n">
-        <v>4.460000038146973</v>
+        <v>4.414999961853027</v>
       </c>
       <c r="C23" t="n">
-        <v>4.550000190734863</v>
+        <v>4.675000190734863</v>
       </c>
       <c r="D23" t="n">
-        <v>4.389999866485596</v>
+        <v>4.349999904632568</v>
       </c>
       <c r="E23" t="n">
-        <v>4.400000095367432</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="F23" t="n">
-        <v>22287800</v>
+        <v>26949500</v>
       </c>
       <c r="G23" t="n">
-        <v>4.65</v>
+        <v>4.634000015258789</v>
       </c>
       <c r="H23" t="n">
-        <v>4.470000028610229</v>
+        <v>4.487500023841858</v>
       </c>
       <c r="I23" t="n">
-        <v>4.653833333651225</v>
+        <v>4.635166668891907</v>
       </c>
       <c r="J23" t="n">
-        <v>4.953041656812032</v>
+        <v>4.943041658401489</v>
       </c>
       <c r="K23" t="n">
-        <v>5.386708328127861</v>
+        <v>5.372916661699613</v>
       </c>
       <c r="L23" t="n">
-        <v>4.470000028610229</v>
+        <v>4.487500023841858</v>
       </c>
       <c r="M23" t="n">
-        <v>4.976089173713814</v>
+        <v>4.987178799622234</v>
       </c>
       <c r="N23" t="n">
-        <v>3.963910883506645</v>
+        <v>3.987821248061482</v>
       </c>
       <c r="O23" t="n">
-        <v>46.2086933314685</v>
+        <v>51.39560930911139</v>
       </c>
       <c r="P23" t="n">
-        <v>22.64380947938978</v>
+        <v>22.26980604459535</v>
       </c>
       <c r="Q23" t="n">
-        <v>21755665</v>
+        <v>20352710</v>
       </c>
       <c r="R23" t="n">
-        <v>1.024459606268069</v>
+        <v>1.324123421401867</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.781584079561353</v>
+        <v>4.772728036257834</v>
       </c>
       <c r="T23" t="n">
-        <v>0.04811098578047535</v>
+        <v>-0.3740034347944281</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2129209937638432</v>
+        <v>-1.651680717128645</v>
       </c>
       <c r="V23" t="n">
-        <v>-9.278346765230062</v>
+        <v>-0.6465459878108537</v>
       </c>
       <c r="W23" t="n">
-        <v>-8.523905453004721</v>
+        <v>-1.705755282089849</v>
       </c>
       <c r="X23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="b">
         <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
+          <t>Bullish-neutral</t>
+        </is>
+      </c>
+      <c r="AA23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AA23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>25.83333333333334</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>Bearish trend bias</t>
-        </is>
-      </c>
       <c r="AR23" t="b">
         <v>0</v>
       </c>
@@ -4384,85 +4384,85 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>Bearish trend bias</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B24" t="n">
-        <v>4.414999961853027</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="C24" t="n">
-        <v>4.675000190734863</v>
+        <v>5.239999771118164</v>
       </c>
       <c r="D24" t="n">
-        <v>4.349999904632568</v>
+        <v>4.619999885559082</v>
       </c>
       <c r="E24" t="n">
-        <v>4.610000133514404</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="F24" t="n">
-        <v>26949500</v>
+        <v>36434600</v>
       </c>
       <c r="G24" t="n">
-        <v>4.634000015258789</v>
+        <v>4.65600004196167</v>
       </c>
       <c r="H24" t="n">
-        <v>4.487500023841858</v>
+        <v>4.515500020980835</v>
       </c>
       <c r="I24" t="n">
-        <v>4.635166668891907</v>
+        <v>4.617166670163472</v>
       </c>
       <c r="J24" t="n">
-        <v>4.943041658401489</v>
+        <v>4.934791660308838</v>
       </c>
       <c r="K24" t="n">
-        <v>5.372916661699613</v>
+        <v>5.363416662812233</v>
       </c>
       <c r="L24" t="n">
-        <v>4.487500023841858</v>
+        <v>4.515500020980835</v>
       </c>
       <c r="M24" t="n">
-        <v>4.987178799622234</v>
+        <v>5.055654911890581</v>
       </c>
       <c r="N24" t="n">
-        <v>3.987821248061482</v>
+        <v>3.975345130071089</v>
       </c>
       <c r="O24" t="n">
-        <v>51.39560930911139</v>
+        <v>58.5666248950925</v>
       </c>
       <c r="P24" t="n">
-        <v>22.26980604459535</v>
+        <v>23.92447739563586</v>
       </c>
       <c r="Q24" t="n">
-        <v>20352710</v>
+        <v>20942990</v>
       </c>
       <c r="R24" t="n">
-        <v>1.324123421401867</v>
+        <v>1.739703834075268</v>
       </c>
       <c r="S24" t="n">
-        <v>4.772728036257834</v>
+        <v>7.592188600778815</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3740034347944281</v>
+        <v>1.654671351040509</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.651680717128645</v>
+        <v>7.430111190582545</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6465459878108537</v>
+        <v>6.209849188764216</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.705755282089849</v>
+        <v>2.268044034585137</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
       <c r="Y24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>23.33333333333333</v>
+        <v>31.66666666666666</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4508,22 +4508,22 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bullish trend bias</t>
         </is>
       </c>
       <c r="AR24" t="b">
@@ -4540,79 +4540,79 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bullish trend bias</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B25" t="n">
-        <v>4.650000095367432</v>
+        <v>4.901999950408936</v>
       </c>
       <c r="C25" t="n">
-        <v>5.239999771118164</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="D25" t="n">
-        <v>4.619999885559082</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="E25" t="n">
-        <v>4.960000038146973</v>
+        <v>4.730000019073486</v>
       </c>
       <c r="F25" t="n">
-        <v>36434600</v>
+        <v>18328700</v>
       </c>
       <c r="G25" t="n">
-        <v>4.65600004196167</v>
+        <v>4.674000072479248</v>
       </c>
       <c r="H25" t="n">
-        <v>4.515500020980835</v>
+        <v>4.534000015258789</v>
       </c>
       <c r="I25" t="n">
-        <v>4.617166670163472</v>
+        <v>4.591000000635783</v>
       </c>
       <c r="J25" t="n">
-        <v>4.934791660308838</v>
+        <v>4.926874995231628</v>
       </c>
       <c r="K25" t="n">
-        <v>5.363416662812233</v>
+        <v>5.351916663845381</v>
       </c>
       <c r="L25" t="n">
-        <v>4.515500020980835</v>
+        <v>4.534000015258789</v>
       </c>
       <c r="M25" t="n">
-        <v>5.055654911890581</v>
+        <v>5.077067277301879</v>
       </c>
       <c r="N25" t="n">
-        <v>3.975345130071089</v>
+        <v>3.990932753215698</v>
       </c>
       <c r="O25" t="n">
-        <v>58.5666248950925</v>
+        <v>53.02969618721632</v>
       </c>
       <c r="P25" t="n">
-        <v>23.92447739563586</v>
+        <v>23.9553268732</v>
       </c>
       <c r="Q25" t="n">
-        <v>20942990</v>
+        <v>20557625</v>
       </c>
       <c r="R25" t="n">
-        <v>1.739703834075268</v>
+        <v>0.8915767263971397</v>
       </c>
       <c r="S25" t="n">
-        <v>7.592188600778815</v>
+        <v>-4.637097123076095</v>
       </c>
       <c r="T25" t="n">
-        <v>1.654671351040509</v>
+        <v>0.0308494775641357</v>
       </c>
       <c r="U25" t="n">
-        <v>7.430111190582545</v>
+        <v>0.1289452515680134</v>
       </c>
       <c r="V25" t="n">
-        <v>6.209849188764216</v>
+        <v>7.499998103488625</v>
       </c>
       <c r="W25" t="n">
-        <v>2.268044034585137</v>
+        <v>1.939658516758924</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
@@ -4626,13 +4626,13 @@
         </is>
       </c>
       <c r="AA25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="b">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>31.66666666666666</v>
+        <v>32.5</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -4652,10 +4652,10 @@
         <v>0</v>
       </c>
       <c r="AI25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK25" t="b">
         <v>0</v>
@@ -4664,13 +4664,13 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>Bullish trend bias</t>
+          <t>Expansion with bullish bias</t>
         </is>
       </c>
       <c r="AR25" t="b">
@@ -4696,79 +4696,79 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>Bullish trend bias</t>
+          <t>Expansion with bullish bias</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B26" t="n">
-        <v>4.901999950408936</v>
+        <v>4.710000038146973</v>
       </c>
       <c r="C26" t="n">
-        <v>4.960000038146973</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="D26" t="n">
-        <v>4.699999809265137</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="E26" t="n">
-        <v>4.730000019073486</v>
+        <v>4.590000152587891</v>
       </c>
       <c r="F26" t="n">
-        <v>18328700</v>
+        <v>15464200</v>
       </c>
       <c r="G26" t="n">
-        <v>4.674000072479248</v>
+        <v>4.658000087738037</v>
       </c>
       <c r="H26" t="n">
-        <v>4.534000015258789</v>
+        <v>4.543500018119812</v>
       </c>
       <c r="I26" t="n">
-        <v>4.591000000635783</v>
+        <v>4.569000005722046</v>
       </c>
       <c r="J26" t="n">
-        <v>4.926874995231628</v>
+        <v>4.916791661580404</v>
       </c>
       <c r="K26" t="n">
-        <v>5.351916663845381</v>
+        <v>5.339166664083799</v>
       </c>
       <c r="L26" t="n">
-        <v>4.534000015258789</v>
+        <v>4.543500018119812</v>
       </c>
       <c r="M26" t="n">
-        <v>5.077067277301879</v>
+        <v>5.083335232450989</v>
       </c>
       <c r="N26" t="n">
-        <v>3.990932753215698</v>
+        <v>4.003664803788635</v>
       </c>
       <c r="O26" t="n">
-        <v>53.02969618721632</v>
+        <v>49.93506574444695</v>
       </c>
       <c r="P26" t="n">
-        <v>23.9553268732</v>
+        <v>23.76296741183116</v>
       </c>
       <c r="Q26" t="n">
-        <v>20557625</v>
+        <v>20859725</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8915767263971397</v>
+        <v>0.7413424673623453</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.637097123076095</v>
+        <v>-2.959828032157574</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0308494775641357</v>
+        <v>-0.192359461368838</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1289452515680134</v>
+        <v>-0.8029924299803204</v>
       </c>
       <c r="V26" t="n">
-        <v>7.499998103488625</v>
+        <v>-0.433839053086249</v>
       </c>
       <c r="W26" t="n">
-        <v>1.939658516758924</v>
+        <v>-1.71306043681142</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
@@ -4778,17 +4778,17 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Bullish-neutral</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AA26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="b">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>32.5</v>
+        <v>30.83333333333334</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4820,22 +4820,22 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>Expansion with bullish bias</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AR26" t="b">
@@ -4852,79 +4852,79 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>Expansion with bullish bias</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B27" t="n">
-        <v>4.710000038146973</v>
+        <v>4.639999866485596</v>
       </c>
       <c r="C27" t="n">
-        <v>4.71999979019165</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="D27" t="n">
-        <v>4.550000190734863</v>
+        <v>4.485000133514404</v>
       </c>
       <c r="E27" t="n">
-        <v>4.590000152587891</v>
+        <v>4.599999904632568</v>
       </c>
       <c r="F27" t="n">
-        <v>15464200</v>
+        <v>15855800</v>
       </c>
       <c r="G27" t="n">
-        <v>4.658000087738037</v>
+        <v>4.698000049591064</v>
       </c>
       <c r="H27" t="n">
-        <v>4.543500018119812</v>
+        <v>4.561000013351441</v>
       </c>
       <c r="I27" t="n">
-        <v>4.569000005722046</v>
+        <v>4.547833339373271</v>
       </c>
       <c r="J27" t="n">
-        <v>4.916791661580404</v>
+        <v>4.909041659037272</v>
       </c>
       <c r="K27" t="n">
-        <v>5.339166664083799</v>
+        <v>5.326416664322218</v>
       </c>
       <c r="L27" t="n">
-        <v>4.543500018119812</v>
+        <v>4.561000013351441</v>
       </c>
       <c r="M27" t="n">
-        <v>5.083335232450989</v>
+        <v>5.083177591208552</v>
       </c>
       <c r="N27" t="n">
-        <v>4.003664803788635</v>
+        <v>4.038822435494329</v>
       </c>
       <c r="O27" t="n">
-        <v>49.93506574444695</v>
+        <v>50.15879587377292</v>
       </c>
       <c r="P27" t="n">
-        <v>23.76296741183116</v>
+        <v>22.89750389513432</v>
       </c>
       <c r="Q27" t="n">
-        <v>20859725</v>
+        <v>20855085</v>
       </c>
       <c r="R27" t="n">
-        <v>0.7413424673623453</v>
+        <v>0.7602846020526888</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.959828032157574</v>
+        <v>0.2178595144281203</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.192359461368838</v>
+        <v>-0.8654635166968347</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.8029924299803204</v>
+        <v>-3.642068356605732</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.433839053086249</v>
+        <v>-7.258067152130476</v>
       </c>
       <c r="W27" t="n">
-        <v>-1.71306043681142</v>
+        <v>4.545450112051319</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
@@ -4934,17 +4934,17 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bullish-neutral</t>
         </is>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>30.83333333333334</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="b">
         <v>0</v>
@@ -4976,10 +4976,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO27" t="n">
         <v>2</v>
@@ -5014,83 +5014,83 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B28" t="n">
         <v>4.639999866485596</v>
       </c>
       <c r="C28" t="n">
-        <v>4.739999771118164</v>
+        <v>4.639999866485596</v>
       </c>
       <c r="D28" t="n">
-        <v>4.485000133514404</v>
+        <v>4.414999961853027</v>
       </c>
       <c r="E28" t="n">
-        <v>4.599999904632568</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="F28" t="n">
-        <v>15855800</v>
+        <v>16212500</v>
       </c>
       <c r="G28" t="n">
-        <v>4.698000049591064</v>
+        <v>4.669999980926514</v>
       </c>
       <c r="H28" t="n">
-        <v>4.561000013351441</v>
+        <v>4.577999997138977</v>
       </c>
       <c r="I28" t="n">
-        <v>4.547833339373271</v>
+        <v>4.528166667620341</v>
       </c>
       <c r="J28" t="n">
-        <v>4.909041659037272</v>
+        <v>4.900624990463257</v>
       </c>
       <c r="K28" t="n">
-        <v>5.326416664322218</v>
+        <v>5.310291662812233</v>
       </c>
       <c r="L28" t="n">
-        <v>4.561000013351441</v>
+        <v>4.577999997138977</v>
       </c>
       <c r="M28" t="n">
-        <v>5.083177591208552</v>
+        <v>5.061826825045111</v>
       </c>
       <c r="N28" t="n">
-        <v>4.038822435494329</v>
+        <v>4.094173169232842</v>
       </c>
       <c r="O28" t="n">
-        <v>50.15879587377292</v>
+        <v>47.20539981816225</v>
       </c>
       <c r="P28" t="n">
-        <v>22.89750389513432</v>
+        <v>21.13703924021416</v>
       </c>
       <c r="Q28" t="n">
-        <v>20855085</v>
+        <v>20437335</v>
       </c>
       <c r="R28" t="n">
-        <v>0.7602846020526888</v>
+        <v>0.7932785757047091</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2178595144281203</v>
+        <v>-2.826089502958407</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.8654635166968347</v>
+        <v>-1.76046465492016</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.642068356605732</v>
+        <v>-7.688456623842976</v>
       </c>
       <c r="V28" t="n">
-        <v>-7.258067152130476</v>
+        <v>-5.496833569416449</v>
       </c>
       <c r="W28" t="n">
-        <v>4.545450112051319</v>
+        <v>-3.036883715142658</v>
       </c>
       <c r="X28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Bullish-neutral</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AA28" t="b">
@@ -5100,18 +5100,18 @@
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>28.33333333333333</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Tight</t>
         </is>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
       <c r="AF28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="b">
         <v>0</v>
@@ -5132,22 +5132,22 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
         <v>3</v>
       </c>
-      <c r="AN28" t="n">
-        <v>1</v>
-      </c>
       <c r="AO28" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Tight range with bearish bias</t>
         </is>
       </c>
       <c r="AR28" t="b">
@@ -5164,79 +5164,79 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Tight range with bearish bias</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B29" t="n">
-        <v>4.639999866485596</v>
+        <v>4.440000057220459</v>
       </c>
       <c r="C29" t="n">
-        <v>4.639999866485596</v>
+        <v>4.480000019073486</v>
       </c>
       <c r="D29" t="n">
-        <v>4.414999961853027</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="E29" t="n">
-        <v>4.46999979019165</v>
+        <v>4.320000171661377</v>
       </c>
       <c r="F29" t="n">
-        <v>16212500</v>
+        <v>17455900</v>
       </c>
       <c r="G29" t="n">
-        <v>4.669999980926514</v>
+        <v>4.542000007629395</v>
       </c>
       <c r="H29" t="n">
-        <v>4.577999997138977</v>
+        <v>4.588499999046325</v>
       </c>
       <c r="I29" t="n">
-        <v>4.528166667620341</v>
+        <v>4.508166670799255</v>
       </c>
       <c r="J29" t="n">
-        <v>4.900624990463257</v>
+        <v>4.891541659832001</v>
       </c>
       <c r="K29" t="n">
-        <v>5.310291662812233</v>
+        <v>5.292874996860822</v>
       </c>
       <c r="L29" t="n">
-        <v>4.577999997138977</v>
+        <v>4.588499999046325</v>
       </c>
       <c r="M29" t="n">
-        <v>5.061826825045111</v>
+        <v>5.037417980994006</v>
       </c>
       <c r="N29" t="n">
-        <v>4.094173169232842</v>
+        <v>4.139582017098645</v>
       </c>
       <c r="O29" t="n">
-        <v>47.20539981816225</v>
+        <v>43.98706877750195</v>
       </c>
       <c r="P29" t="n">
-        <v>21.13703924021416</v>
+        <v>19.56709085936508</v>
       </c>
       <c r="Q29" t="n">
-        <v>20437335</v>
+        <v>20408940</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7932785757047091</v>
+        <v>0.8553065470328199</v>
       </c>
       <c r="S29" t="n">
-        <v>-2.826089502958407</v>
+        <v>-3.355696321494506</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.76046465492016</v>
+        <v>-1.56994838084908</v>
       </c>
       <c r="U29" t="n">
-        <v>-7.688456623842976</v>
+        <v>-7.427475357391511</v>
       </c>
       <c r="V29" t="n">
-        <v>-5.496833569416449</v>
+        <v>-5.882352330081842</v>
       </c>
       <c r="W29" t="n">
-        <v>-3.036883715142658</v>
+        <v>-12.90322301539126</v>
       </c>
       <c r="X29" t="b">
         <v>0</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish-neutral</t>
         </is>
       </c>
       <c r="AA29" t="b">
@@ -5256,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>19.16666666666667</v>
+        <v>12.5</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO29" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -5326,73 +5326,73 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B30" t="n">
-        <v>4.440000057220459</v>
+        <v>4.264999866485596</v>
       </c>
       <c r="C30" t="n">
-        <v>4.480000019073486</v>
+        <v>4.34499979019165</v>
       </c>
       <c r="D30" t="n">
-        <v>4.300000190734863</v>
+        <v>4.159999847412109</v>
       </c>
       <c r="E30" t="n">
-        <v>4.320000171661377</v>
+        <v>4.190000057220459</v>
       </c>
       <c r="F30" t="n">
-        <v>17455900</v>
+        <v>19769400</v>
       </c>
       <c r="G30" t="n">
-        <v>4.542000007629395</v>
+        <v>4.434000015258789</v>
       </c>
       <c r="H30" t="n">
-        <v>4.588499999046325</v>
+        <v>4.593499994277954</v>
       </c>
       <c r="I30" t="n">
-        <v>4.508166670799255</v>
+        <v>4.487333337465922</v>
       </c>
       <c r="J30" t="n">
-        <v>4.891541659832001</v>
+        <v>4.881791659196218</v>
       </c>
       <c r="K30" t="n">
-        <v>5.292874996860822</v>
+        <v>5.266458331545194</v>
       </c>
       <c r="L30" t="n">
-        <v>4.588499999046325</v>
+        <v>4.593499994277954</v>
       </c>
       <c r="M30" t="n">
-        <v>5.037417980994006</v>
+        <v>5.020744541930812</v>
       </c>
       <c r="N30" t="n">
-        <v>4.139582017098645</v>
+        <v>4.166255446625096</v>
       </c>
       <c r="O30" t="n">
-        <v>43.98706877750195</v>
+        <v>41.35552365354274</v>
       </c>
       <c r="P30" t="n">
-        <v>19.56709085936508</v>
+        <v>18.60213554740697</v>
       </c>
       <c r="Q30" t="n">
-        <v>20408940</v>
+        <v>20636540</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8553065470328199</v>
+        <v>0.9579803591105873</v>
       </c>
       <c r="S30" t="n">
-        <v>-3.355696321494506</v>
+        <v>-3.009261788777262</v>
       </c>
       <c r="T30" t="n">
-        <v>-1.56994838084908</v>
+        <v>-0.9649553119581178</v>
       </c>
       <c r="U30" t="n">
-        <v>-7.427475357391511</v>
+        <v>-4.931521598655408</v>
       </c>
       <c r="V30" t="n">
-        <v>-5.882352330081842</v>
+        <v>-8.913040345918411</v>
       </c>
       <c r="W30" t="n">
-        <v>-12.90322301539126</v>
+        <v>-11.4164896337316</v>
       </c>
       <c r="X30" t="b">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>12.5</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -5482,73 +5482,73 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B31" t="n">
-        <v>4.264999866485596</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="C31" t="n">
-        <v>4.34499979019165</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="D31" t="n">
-        <v>4.159999847412109</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="E31" t="n">
-        <v>4.190000057220459</v>
+        <v>4.179999828338623</v>
       </c>
       <c r="F31" t="n">
-        <v>19769400</v>
+        <v>17443800</v>
       </c>
       <c r="G31" t="n">
-        <v>4.434000015258789</v>
+        <v>4.351999950408936</v>
       </c>
       <c r="H31" t="n">
-        <v>4.593499994277954</v>
+        <v>4.592499995231629</v>
       </c>
       <c r="I31" t="n">
-        <v>4.487333337465922</v>
+        <v>4.473666667938232</v>
       </c>
       <c r="J31" t="n">
-        <v>4.881791659196218</v>
+        <v>4.872541658083597</v>
       </c>
       <c r="K31" t="n">
-        <v>5.266458331545194</v>
+        <v>5.23954166273276</v>
       </c>
       <c r="L31" t="n">
-        <v>4.593499994277954</v>
+        <v>4.592499995231629</v>
       </c>
       <c r="M31" t="n">
-        <v>5.020744541930812</v>
+        <v>5.023697845359455</v>
       </c>
       <c r="N31" t="n">
-        <v>4.166255446625096</v>
+        <v>4.161302145103803</v>
       </c>
       <c r="O31" t="n">
-        <v>41.35552365354274</v>
+        <v>41.15157392188054</v>
       </c>
       <c r="P31" t="n">
-        <v>18.60213554740697</v>
+        <v>18.77834950791668</v>
       </c>
       <c r="Q31" t="n">
-        <v>20636540</v>
+        <v>20697370</v>
       </c>
       <c r="R31" t="n">
-        <v>0.9579803591105873</v>
+        <v>0.842802732907611</v>
       </c>
       <c r="S31" t="n">
-        <v>-3.009261788777262</v>
+        <v>-0.2386689438011569</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.9649553119581178</v>
+        <v>0.1762139605097097</v>
       </c>
       <c r="U31" t="n">
-        <v>-4.931521598655408</v>
+        <v>0.9472781233134997</v>
       </c>
       <c r="V31" t="n">
-        <v>-8.913040345918411</v>
+        <v>-6.487695200553767</v>
       </c>
       <c r="W31" t="n">
-        <v>-11.4164896337316</v>
+        <v>-8.932468640945579</v>
       </c>
       <c r="X31" t="b">
         <v>0</v>
@@ -5565,10 +5565,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>11.66666666666667</v>
+        <v>12.5</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="b">
         <v>0</v>
@@ -5603,14 +5603,14 @@
         <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -5638,73 +5638,73 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B32" t="n">
-        <v>4.119999885559082</v>
+        <v>4.215000152587891</v>
       </c>
       <c r="C32" t="n">
-        <v>4.260000228881836</v>
+        <v>4.284999847412109</v>
       </c>
       <c r="D32" t="n">
-        <v>4.079999923706055</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="E32" t="n">
-        <v>4.179999828338623</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="F32" t="n">
-        <v>17443800</v>
+        <v>23496500</v>
       </c>
       <c r="G32" t="n">
-        <v>4.351999950408936</v>
+        <v>4.251999950408935</v>
       </c>
       <c r="H32" t="n">
-        <v>4.592499995231629</v>
+        <v>4.578999996185303</v>
       </c>
       <c r="I32" t="n">
-        <v>4.473666667938232</v>
+        <v>4.459333332379659</v>
       </c>
       <c r="J32" t="n">
-        <v>4.872541658083597</v>
+        <v>4.861624991893768</v>
       </c>
       <c r="K32" t="n">
-        <v>5.23954166273276</v>
+        <v>5.2113333294789</v>
       </c>
       <c r="L32" t="n">
-        <v>4.592499995231629</v>
+        <v>4.578999996185303</v>
       </c>
       <c r="M32" t="n">
-        <v>5.023697845359455</v>
+        <v>5.054190833026862</v>
       </c>
       <c r="N32" t="n">
-        <v>4.161302145103803</v>
+        <v>4.103809159343744</v>
       </c>
       <c r="O32" t="n">
-        <v>41.15157392188054</v>
+        <v>39.4744319817522</v>
       </c>
       <c r="P32" t="n">
-        <v>18.77834950791668</v>
+        <v>20.75522329056273</v>
       </c>
       <c r="Q32" t="n">
-        <v>20697370</v>
+        <v>20991300</v>
       </c>
       <c r="R32" t="n">
-        <v>0.842802732907611</v>
+        <v>1.119344680891607</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.2386689438011569</v>
+        <v>-1.913873851469783</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1762139605097097</v>
+        <v>1.976873782646052</v>
       </c>
       <c r="U32" t="n">
-        <v>0.9472781233134997</v>
+        <v>10.52740967363841</v>
       </c>
       <c r="V32" t="n">
-        <v>-6.487695200553767</v>
+        <v>-5.092598571453333</v>
       </c>
       <c r="W32" t="n">
-        <v>-8.932468640945579</v>
+        <v>-10.86956544273968</v>
       </c>
       <c r="X32" t="b">
         <v>0</v>
@@ -5714,17 +5714,17 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>Bearish-neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="AA32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="b">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>12.5</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AH32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
@@ -5759,10 +5759,10 @@
         <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AO32" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -5794,73 +5794,73 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B33" t="n">
-        <v>4.215000152587891</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="C33" t="n">
-        <v>4.284999847412109</v>
+        <v>4.125</v>
       </c>
       <c r="D33" t="n">
-        <v>3.960000038146973</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="E33" t="n">
-        <v>4.099999904632568</v>
+        <v>3.900000095367432</v>
       </c>
       <c r="F33" t="n">
-        <v>23496500</v>
+        <v>36835900</v>
       </c>
       <c r="G33" t="n">
-        <v>4.251999950408935</v>
+        <v>4.138000011444092</v>
       </c>
       <c r="H33" t="n">
-        <v>4.578999996185303</v>
+        <v>4.546499991416932</v>
       </c>
       <c r="I33" t="n">
-        <v>4.459333332379659</v>
+        <v>4.447333335876465</v>
       </c>
       <c r="J33" t="n">
-        <v>4.861624991893768</v>
+        <v>4.846624994277954</v>
       </c>
       <c r="K33" t="n">
-        <v>5.2113333294789</v>
+        <v>5.184458328286807</v>
       </c>
       <c r="L33" t="n">
-        <v>4.578999996185303</v>
+        <v>4.546499991416932</v>
       </c>
       <c r="M33" t="n">
-        <v>5.054190833026862</v>
+        <v>5.11063042512736</v>
       </c>
       <c r="N33" t="n">
-        <v>4.103809159343744</v>
+        <v>3.982369557706502</v>
       </c>
       <c r="O33" t="n">
-        <v>39.4744319817522</v>
+        <v>35.5713440433594</v>
       </c>
       <c r="P33" t="n">
-        <v>20.75522329056273</v>
+        <v>24.81603144288651</v>
       </c>
       <c r="Q33" t="n">
-        <v>20991300</v>
+        <v>21674195</v>
       </c>
       <c r="R33" t="n">
-        <v>1.119344680891607</v>
+        <v>1.699527940945442</v>
       </c>
       <c r="S33" t="n">
-        <v>-1.913873851469783</v>
+        <v>-4.878044241882973</v>
       </c>
       <c r="T33" t="n">
-        <v>1.976873782646052</v>
+        <v>4.060808152323784</v>
       </c>
       <c r="U33" t="n">
-        <v>10.52740967363841</v>
+        <v>19.56523471453187</v>
       </c>
       <c r="V33" t="n">
-        <v>-5.092598571453333</v>
+        <v>-6.921240045170918</v>
       </c>
       <c r="W33" t="n">
-        <v>-10.86956544273968</v>
+        <v>-12.7516716236754</v>
       </c>
       <c r="X33" t="b">
         <v>0</v>
@@ -5880,18 +5880,18 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>19.16666666666667</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Tight</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
       <c r="AF33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -5903,22 +5903,22 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="b">
         <v>0</v>
       </c>
       <c r="AL33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM33" t="n">
         <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO33" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>Tight range with bearish bias</t>
+          <t>Bearish breakdown candidate</t>
         </is>
       </c>
       <c r="AR33" t="b">
@@ -5944,79 +5944,79 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>Tight range with bearish bias</t>
+          <t>Bearish breakdown candidate</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B34" t="n">
-        <v>4.119999885559082</v>
+        <v>3.789999961853027</v>
       </c>
       <c r="C34" t="n">
-        <v>4.125</v>
+        <v>3.875</v>
       </c>
       <c r="D34" t="n">
-        <v>3.710000038146973</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="E34" t="n">
-        <v>3.900000095367432</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="F34" t="n">
-        <v>36835900</v>
+        <v>40627200</v>
       </c>
       <c r="G34" t="n">
-        <v>4.138000011444092</v>
+        <v>3.985999965667725</v>
       </c>
       <c r="H34" t="n">
-        <v>4.546499991416932</v>
+        <v>4.481499981880188</v>
       </c>
       <c r="I34" t="n">
-        <v>4.447333335876465</v>
+        <v>4.429666670163472</v>
       </c>
       <c r="J34" t="n">
-        <v>4.846624994277954</v>
+        <v>4.829291661580403</v>
       </c>
       <c r="K34" t="n">
-        <v>5.184458328286807</v>
+        <v>5.160624995827675</v>
       </c>
       <c r="L34" t="n">
-        <v>4.546499991416932</v>
+        <v>4.481499981880188</v>
       </c>
       <c r="M34" t="n">
-        <v>5.11063042512736</v>
+        <v>5.177663139813569</v>
       </c>
       <c r="N34" t="n">
-        <v>3.982369557706502</v>
+        <v>3.785336823946808</v>
       </c>
       <c r="O34" t="n">
-        <v>35.5713440433594</v>
+        <v>30.11917053636733</v>
       </c>
       <c r="P34" t="n">
-        <v>24.81603144288651</v>
+        <v>31.06831019739551</v>
       </c>
       <c r="Q34" t="n">
-        <v>21674195</v>
+        <v>22049720</v>
       </c>
       <c r="R34" t="n">
-        <v>1.699527940945442</v>
+        <v>1.84252679852624</v>
       </c>
       <c r="S34" t="n">
-        <v>-4.878044241882973</v>
+        <v>-8.717952417277019</v>
       </c>
       <c r="T34" t="n">
-        <v>4.060808152323784</v>
+        <v>6.252278754509</v>
       </c>
       <c r="U34" t="n">
-        <v>19.56523471453187</v>
+        <v>25.19451496061513</v>
       </c>
       <c r="V34" t="n">
-        <v>-6.921240045170918</v>
+        <v>-14.83253375647879</v>
       </c>
       <c r="W34" t="n">
-        <v>-12.7516716236754</v>
+        <v>-17.59259719171623</v>
       </c>
       <c r="X34" t="b">
         <v>0</v>
@@ -6036,7 +6036,7 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>40.83333333333334</v>
+        <v>70.83333333333334</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
@@ -6071,10 +6071,10 @@
         <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO34" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="AS34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT34" t="b">
         <v>0</v>
@@ -6100,79 +6100,79 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>Bearish breakdown candidate</t>
+          <t>Bearish breakdown confirmed</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B35" t="n">
-        <v>3.789999961853027</v>
+        <v>3.740000009536743</v>
       </c>
       <c r="C35" t="n">
-        <v>3.875</v>
+        <v>4.019999980926514</v>
       </c>
       <c r="D35" t="n">
-        <v>3.539999961853027</v>
+        <v>3.690000057220459</v>
       </c>
       <c r="E35" t="n">
-        <v>3.559999942779541</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="F35" t="n">
-        <v>40627200</v>
+        <v>26273100</v>
       </c>
       <c r="G35" t="n">
-        <v>3.985999965667725</v>
+        <v>3.94399995803833</v>
       </c>
       <c r="H35" t="n">
-        <v>4.481499981880188</v>
+        <v>4.445499992370605</v>
       </c>
       <c r="I35" t="n">
-        <v>4.429666670163472</v>
+        <v>4.420833333333333</v>
       </c>
       <c r="J35" t="n">
-        <v>4.829291661580403</v>
+        <v>4.814374995231629</v>
       </c>
       <c r="K35" t="n">
-        <v>5.160624995827675</v>
+        <v>5.139708329240481</v>
       </c>
       <c r="L35" t="n">
-        <v>4.481499981880188</v>
+        <v>4.445499992370605</v>
       </c>
       <c r="M35" t="n">
-        <v>5.177663139813569</v>
+        <v>5.168053210944125</v>
       </c>
       <c r="N35" t="n">
-        <v>3.785336823946808</v>
+        <v>3.722946773797086</v>
       </c>
       <c r="O35" t="n">
-        <v>30.11917053636733</v>
+        <v>41.95478382381998</v>
       </c>
       <c r="P35" t="n">
-        <v>31.06831019739551</v>
+        <v>32.5071744376817</v>
       </c>
       <c r="Q35" t="n">
-        <v>22049720</v>
+        <v>22504015</v>
       </c>
       <c r="R35" t="n">
-        <v>1.84252679852624</v>
+        <v>1.167485002120733</v>
       </c>
       <c r="S35" t="n">
-        <v>-8.717952417277019</v>
+        <v>11.79775514170436</v>
       </c>
       <c r="T35" t="n">
-        <v>6.252278754509</v>
+        <v>1.438864240286186</v>
       </c>
       <c r="U35" t="n">
-        <v>25.19451496061513</v>
+        <v>4.63129224326726</v>
       </c>
       <c r="V35" t="n">
-        <v>-14.83253375647879</v>
+        <v>-2.92682654512979</v>
       </c>
       <c r="W35" t="n">
-        <v>-17.59259719171623</v>
+        <v>-5.011934016208142</v>
       </c>
       <c r="X35" t="b">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bearish-neutral</t>
         </is>
       </c>
       <c r="AA35" t="b">
@@ -6192,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>70.83333333333334</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
@@ -6209,126 +6209,126 @@
         <v>0</v>
       </c>
       <c r="AH35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="b">
         <v>0</v>
       </c>
       <c r="AL35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AO35" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>Bearish breakdown candidate</t>
+          <t>Expansion with bearish bias</t>
         </is>
       </c>
       <c r="AR35" t="b">
         <v>0</v>
       </c>
       <c r="AS35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="b">
         <v>0</v>
       </c>
       <c r="AU35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>Bearish breakdown confirmed</t>
+          <t>Failed bearish breakdown</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B36" t="n">
-        <v>3.740000009536743</v>
+        <v>3.950000047683716</v>
       </c>
       <c r="C36" t="n">
-        <v>4.019999980926514</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>3.690000057220459</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="E36" t="n">
         <v>3.980000019073486</v>
       </c>
       <c r="F36" t="n">
-        <v>26273100</v>
+        <v>14183600</v>
       </c>
       <c r="G36" t="n">
-        <v>3.94399995803833</v>
+        <v>3.903999996185303</v>
       </c>
       <c r="H36" t="n">
-        <v>4.445499992370605</v>
+        <v>4.411500000953675</v>
       </c>
       <c r="I36" t="n">
-        <v>4.420833333333333</v>
+        <v>4.408666666348775</v>
       </c>
       <c r="J36" t="n">
-        <v>4.814374995231629</v>
+        <v>4.801541662216186</v>
       </c>
       <c r="K36" t="n">
-        <v>5.139708329240481</v>
+        <v>5.122374994556109</v>
       </c>
       <c r="L36" t="n">
-        <v>4.445499992370605</v>
+        <v>4.411500000953675</v>
       </c>
       <c r="M36" t="n">
-        <v>5.168053210944125</v>
+        <v>5.155239489716097</v>
       </c>
       <c r="N36" t="n">
-        <v>3.722946773797086</v>
+        <v>3.667760512191252</v>
       </c>
       <c r="O36" t="n">
         <v>41.95478382381998</v>
       </c>
       <c r="P36" t="n">
-        <v>32.5071744376817</v>
+        <v>33.71821324273564</v>
       </c>
       <c r="Q36" t="n">
-        <v>22504015</v>
+        <v>22444130</v>
       </c>
       <c r="R36" t="n">
-        <v>1.167485002120733</v>
+        <v>0.6319514278343602</v>
       </c>
       <c r="S36" t="n">
-        <v>11.79775514170436</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1.438864240286186</v>
+        <v>1.211038805053946</v>
       </c>
       <c r="U36" t="n">
-        <v>4.63129224326726</v>
+        <v>3.725450845860445</v>
       </c>
       <c r="V36" t="n">
-        <v>-2.92682654512979</v>
+        <v>2.051280044866699</v>
       </c>
       <c r="W36" t="n">
-        <v>-5.011934016208142</v>
+        <v>-4.784684628674452</v>
       </c>
       <c r="X36" t="b">
         <v>0</v>
@@ -6348,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>76.66666666666667</v>
+        <v>79.16666666666666</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="AI36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="b">
         <v>0</v>
@@ -6408,83 +6408,83 @@
         <v>0</v>
       </c>
       <c r="AU36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>Failed bearish breakdown</t>
+          <t>Expansion with bearish bias</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B37" t="n">
-        <v>3.950000047683716</v>
+        <v>4.005000114440918</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>4.089000225067139</v>
       </c>
       <c r="D37" t="n">
+        <v>3.839999914169311</v>
+      </c>
+      <c r="E37" t="n">
         <v>3.849999904632568</v>
       </c>
-      <c r="E37" t="n">
-        <v>3.980000019073486</v>
-      </c>
       <c r="F37" t="n">
-        <v>14183600</v>
+        <v>11126700</v>
       </c>
       <c r="G37" t="n">
-        <v>3.903999996185303</v>
+        <v>3.853999996185302</v>
       </c>
       <c r="H37" t="n">
-        <v>4.411500000953675</v>
+        <v>4.363499999046326</v>
       </c>
       <c r="I37" t="n">
-        <v>4.408666666348775</v>
+        <v>4.395333329836528</v>
       </c>
       <c r="J37" t="n">
-        <v>4.801541662216186</v>
+        <v>4.791208326816559</v>
       </c>
       <c r="K37" t="n">
-        <v>5.122374994556109</v>
+        <v>5.103666660189629</v>
       </c>
       <c r="L37" t="n">
-        <v>4.411500000953675</v>
+        <v>4.363499999046326</v>
       </c>
       <c r="M37" t="n">
-        <v>5.155239489716097</v>
+        <v>5.122703900623581</v>
       </c>
       <c r="N37" t="n">
-        <v>3.667760512191252</v>
+        <v>3.60429609746907</v>
       </c>
       <c r="O37" t="n">
-        <v>41.95478382381998</v>
+        <v>39.55017280477261</v>
       </c>
       <c r="P37" t="n">
-        <v>33.71821324273564</v>
+        <v>34.79793293196678</v>
       </c>
       <c r="Q37" t="n">
-        <v>22444130</v>
+        <v>21765490</v>
       </c>
       <c r="R37" t="n">
-        <v>0.6319514278343602</v>
+        <v>0.5112083394400954</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>-3.26633451803805</v>
       </c>
       <c r="T37" t="n">
-        <v>1.211038805053946</v>
+        <v>1.079719689231133</v>
       </c>
       <c r="U37" t="n">
-        <v>3.725450845860445</v>
+        <v>3.202185363317711</v>
       </c>
       <c r="V37" t="n">
-        <v>2.051280044866699</v>
+        <v>8.146066475119195</v>
       </c>
       <c r="W37" t="n">
-        <v>-4.784684628674452</v>
+        <v>-6.097561117441163</v>
       </c>
       <c r="X37" t="b">
         <v>0</v>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Bearish-neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="AA37" t="b">
@@ -6504,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>79.16666666666666</v>
+        <v>80</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="b">
         <v>0</v>
@@ -6536,10 +6536,10 @@
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO37" t="n">
         <v>-4</v>
@@ -6574,73 +6574,73 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B38" t="n">
-        <v>4.005000114440918</v>
+        <v>3.869999885559082</v>
       </c>
       <c r="C38" t="n">
-        <v>4.089000225067139</v>
+        <v>3.880000114440918</v>
       </c>
       <c r="D38" t="n">
-        <v>3.839999914169311</v>
+        <v>3.640000104904175</v>
       </c>
       <c r="E38" t="n">
-        <v>3.849999904632568</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="F38" t="n">
-        <v>11126700</v>
+        <v>24045200</v>
       </c>
       <c r="G38" t="n">
-        <v>3.853999996185302</v>
+        <v>3.815999984741211</v>
       </c>
       <c r="H38" t="n">
-        <v>4.363499999046326</v>
+        <v>4.314499998092652</v>
       </c>
       <c r="I38" t="n">
-        <v>4.395333329836528</v>
+        <v>4.384999998410543</v>
       </c>
       <c r="J38" t="n">
-        <v>4.791208326816559</v>
+        <v>4.782374993960063</v>
       </c>
       <c r="K38" t="n">
-        <v>5.103666660189629</v>
+        <v>5.087166660030683</v>
       </c>
       <c r="L38" t="n">
-        <v>4.363499999046326</v>
+        <v>4.314499998092652</v>
       </c>
       <c r="M38" t="n">
-        <v>5.122703900623581</v>
+        <v>5.110581862283788</v>
       </c>
       <c r="N38" t="n">
-        <v>3.60429609746907</v>
+        <v>3.518418133901515</v>
       </c>
       <c r="O38" t="n">
-        <v>39.55017280477261</v>
+        <v>37.08509138101662</v>
       </c>
       <c r="P38" t="n">
-        <v>34.79793293196678</v>
+        <v>36.90262438489128</v>
       </c>
       <c r="Q38" t="n">
-        <v>21765490</v>
+        <v>22017930</v>
       </c>
       <c r="R38" t="n">
-        <v>0.5112083394400954</v>
+        <v>1.092073596382584</v>
       </c>
       <c r="S38" t="n">
-        <v>-3.26633451803805</v>
+        <v>-3.636360258532434</v>
       </c>
       <c r="T38" t="n">
-        <v>1.079719689231133</v>
+        <v>2.104691452924506</v>
       </c>
       <c r="U38" t="n">
-        <v>3.202185363317711</v>
+        <v>6.048323206551887</v>
       </c>
       <c r="V38" t="n">
-        <v>8.146066475119195</v>
+        <v>-6.783919086245827</v>
       </c>
       <c r="W38" t="n">
-        <v>-6.097561117441163</v>
+        <v>-4.871796219855195</v>
       </c>
       <c r="X38" t="b">
         <v>0</v>
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>80</v>
+        <v>80.83333333333333</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
@@ -6692,17 +6692,17 @@
         <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO38" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -6730,73 +6730,73 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B39" t="n">
-        <v>3.869999885559082</v>
+        <v>3.740000009536743</v>
       </c>
       <c r="C39" t="n">
-        <v>3.880000114440918</v>
+        <v>3.75</v>
       </c>
       <c r="D39" t="n">
-        <v>3.640000104904175</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="E39" t="n">
-        <v>3.710000038146973</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="F39" t="n">
-        <v>24045200</v>
+        <v>19051500</v>
       </c>
       <c r="G39" t="n">
-        <v>3.815999984741211</v>
+        <v>3.819999980926513</v>
       </c>
       <c r="H39" t="n">
-        <v>4.314499998092652</v>
+        <v>4.250999999046326</v>
       </c>
       <c r="I39" t="n">
-        <v>4.384999998410543</v>
+        <v>4.375666666030884</v>
       </c>
       <c r="J39" t="n">
-        <v>4.782374993960063</v>
+        <v>4.772374991575877</v>
       </c>
       <c r="K39" t="n">
-        <v>5.087166660030683</v>
+        <v>5.070791658759117</v>
       </c>
       <c r="L39" t="n">
-        <v>4.314499998092652</v>
+        <v>4.250999999046326</v>
       </c>
       <c r="M39" t="n">
-        <v>5.110581862283788</v>
+        <v>5.069519882820972</v>
       </c>
       <c r="N39" t="n">
-        <v>3.518418133901515</v>
+        <v>3.432480115271681</v>
       </c>
       <c r="O39" t="n">
-        <v>37.08509138101662</v>
+        <v>34.90926430671229</v>
       </c>
       <c r="P39" t="n">
-        <v>36.90262438489128</v>
+        <v>38.50952171057507</v>
       </c>
       <c r="Q39" t="n">
-        <v>22017930</v>
+        <v>22122765</v>
       </c>
       <c r="R39" t="n">
-        <v>1.092073596382584</v>
+        <v>0.8611717387044522</v>
       </c>
       <c r="S39" t="n">
-        <v>-3.636360258532434</v>
+        <v>-3.504046175316189</v>
       </c>
       <c r="T39" t="n">
-        <v>2.104691452924506</v>
+        <v>1.606897325683789</v>
       </c>
       <c r="U39" t="n">
-        <v>6.048323206551887</v>
+        <v>4.354425606493417</v>
       </c>
       <c r="V39" t="n">
-        <v>-6.783919086245827</v>
+        <v>-10.05025360428387</v>
       </c>
       <c r="W39" t="n">
-        <v>-4.871796219855195</v>
+        <v>0.5617972260667514</v>
       </c>
       <c r="X39" t="b">
         <v>0</v>
@@ -6816,7 +6816,7 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>80.83333333333333</v>
+        <v>81.66666666666667</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
@@ -6886,73 +6886,73 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B40" t="n">
-        <v>3.740000009536743</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="C40" t="n">
-        <v>3.75</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="D40" t="n">
+        <v>3.450000047683716</v>
+      </c>
+      <c r="E40" t="n">
         <v>3.490000009536743</v>
       </c>
-      <c r="E40" t="n">
-        <v>3.579999923706055</v>
-      </c>
       <c r="F40" t="n">
-        <v>19051500</v>
+        <v>16161000</v>
       </c>
       <c r="G40" t="n">
-        <v>3.819999980926513</v>
+        <v>3.721999979019165</v>
       </c>
       <c r="H40" t="n">
-        <v>4.250999999046326</v>
+        <v>4.193500006198883</v>
       </c>
       <c r="I40" t="n">
-        <v>4.375666666030884</v>
+        <v>4.365166668097178</v>
       </c>
       <c r="J40" t="n">
-        <v>4.772374991575877</v>
+        <v>4.760291657845179</v>
       </c>
       <c r="K40" t="n">
-        <v>5.070791658759117</v>
+        <v>5.057874991496404</v>
       </c>
       <c r="L40" t="n">
-        <v>4.250999999046326</v>
+        <v>4.193500006198883</v>
       </c>
       <c r="M40" t="n">
-        <v>5.069519882820972</v>
+        <v>5.057280607515944</v>
       </c>
       <c r="N40" t="n">
-        <v>3.432480115271681</v>
+        <v>3.329719404881823</v>
       </c>
       <c r="O40" t="n">
-        <v>34.90926430671229</v>
+        <v>33.44622764731281</v>
       </c>
       <c r="P40" t="n">
-        <v>38.50952171057507</v>
+        <v>41.19616549613495</v>
       </c>
       <c r="Q40" t="n">
-        <v>22122765</v>
+        <v>21971680</v>
       </c>
       <c r="R40" t="n">
-        <v>0.8611717387044522</v>
+        <v>0.7355377467722086</v>
       </c>
       <c r="S40" t="n">
-        <v>-3.504046175316189</v>
+        <v>-2.513964136517144</v>
       </c>
       <c r="T40" t="n">
-        <v>1.606897325683789</v>
+        <v>2.686643785559873</v>
       </c>
       <c r="U40" t="n">
-        <v>4.354425606493417</v>
+        <v>6.976570121415193</v>
       </c>
       <c r="V40" t="n">
-        <v>-10.05025360428387</v>
+        <v>-9.35064685748822</v>
       </c>
       <c r="W40" t="n">
-        <v>0.5617972260667514</v>
+        <v>-12.31155796956029</v>
       </c>
       <c r="X40" t="b">
         <v>0</v>
@@ -6972,7 +6972,7 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>81.66666666666667</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -7042,73 +7042,73 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B41" t="n">
-        <v>3.599999904632568</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="C41" t="n">
-        <v>3.720000028610229</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="D41" t="n">
-        <v>3.450000047683716</v>
+        <v>3.309999942779541</v>
       </c>
       <c r="E41" t="n">
-        <v>3.490000009536743</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="F41" t="n">
-        <v>16161000</v>
+        <v>17316000</v>
       </c>
       <c r="G41" t="n">
-        <v>3.721999979019165</v>
+        <v>3.617999982833862</v>
       </c>
       <c r="H41" t="n">
-        <v>4.193500006198883</v>
+        <v>4.133000004291534</v>
       </c>
       <c r="I41" t="n">
-        <v>4.365166668097178</v>
+        <v>4.353500004609426</v>
       </c>
       <c r="J41" t="n">
-        <v>4.760291657845179</v>
+        <v>4.748874992132187</v>
       </c>
       <c r="K41" t="n">
-        <v>5.057874991496404</v>
+        <v>5.045333325862885</v>
       </c>
       <c r="L41" t="n">
-        <v>4.193500006198883</v>
+        <v>4.133000004291534</v>
       </c>
       <c r="M41" t="n">
-        <v>5.057280607515944</v>
+        <v>5.025285099865482</v>
       </c>
       <c r="N41" t="n">
-        <v>3.329719404881823</v>
+        <v>3.240714908717586</v>
       </c>
       <c r="O41" t="n">
-        <v>33.44622764731281</v>
+        <v>32.95050358832657</v>
       </c>
       <c r="P41" t="n">
-        <v>41.19616549613495</v>
+        <v>43.17856736740559</v>
       </c>
       <c r="Q41" t="n">
-        <v>21971680</v>
+        <v>21765945</v>
       </c>
       <c r="R41" t="n">
-        <v>0.7355377467722086</v>
+        <v>0.7955547071353897</v>
       </c>
       <c r="S41" t="n">
-        <v>-2.513964136517144</v>
+        <v>-0.859598031741915</v>
       </c>
       <c r="T41" t="n">
-        <v>2.686643785559873</v>
+        <v>1.982401871270646</v>
       </c>
       <c r="U41" t="n">
-        <v>6.976570121415193</v>
+        <v>4.812102892092307</v>
       </c>
       <c r="V41" t="n">
-        <v>-9.35064685748822</v>
+        <v>-6.738544405106451</v>
       </c>
       <c r="W41" t="n">
-        <v>-12.31155796956029</v>
+        <v>-13.06532609131911</v>
       </c>
       <c r="X41" t="b">
         <v>0</v>
@@ -7128,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>83.33333333333334</v>
+        <v>85</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="b">
         <v>0</v>
@@ -7198,73 +7198,73 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B42" t="n">
-        <v>3.480000019073486</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="C42" t="n">
-        <v>3.490000009536743</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="D42" t="n">
-        <v>3.309999942779541</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="E42" t="n">
-        <v>3.460000038146973</v>
+        <v>3.529999971389771</v>
       </c>
       <c r="F42" t="n">
-        <v>17316000</v>
+        <v>38592800</v>
       </c>
       <c r="G42" t="n">
-        <v>3.617999982833862</v>
+        <v>3.553999996185303</v>
       </c>
       <c r="H42" t="n">
-        <v>4.133000004291534</v>
+        <v>4.089499998092651</v>
       </c>
       <c r="I42" t="n">
-        <v>4.353500004609426</v>
+        <v>4.34516666730245</v>
       </c>
       <c r="J42" t="n">
-        <v>4.748874992132187</v>
+        <v>4.738041659196218</v>
       </c>
       <c r="K42" t="n">
-        <v>5.045333325862885</v>
+        <v>5.032624992728233</v>
       </c>
       <c r="L42" t="n">
-        <v>4.133000004291534</v>
+        <v>4.089499998092651</v>
       </c>
       <c r="M42" t="n">
-        <v>5.025285099865482</v>
+        <v>5.011316884376432</v>
       </c>
       <c r="N42" t="n">
-        <v>3.240714908717586</v>
+        <v>3.16768311180887</v>
       </c>
       <c r="O42" t="n">
-        <v>32.95050358832657</v>
+        <v>35.35801849549452</v>
       </c>
       <c r="P42" t="n">
-        <v>43.17856736740559</v>
+        <v>45.08213164023563</v>
       </c>
       <c r="Q42" t="n">
-        <v>21765945</v>
+        <v>22581195</v>
       </c>
       <c r="R42" t="n">
-        <v>0.7955547071353897</v>
+        <v>1.709068098477516</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.859598031741915</v>
+        <v>2.023119435579157</v>
       </c>
       <c r="T42" t="n">
-        <v>1.982401871270646</v>
+        <v>1.903564272830039</v>
       </c>
       <c r="U42" t="n">
-        <v>4.812102892092307</v>
+        <v>4.408585992751091</v>
       </c>
       <c r="V42" t="n">
-        <v>-6.738544405106451</v>
+        <v>-1.396646742509522</v>
       </c>
       <c r="W42" t="n">
-        <v>-13.06532609131911</v>
+        <v>-8.311686783621807</v>
       </c>
       <c r="X42" t="b">
         <v>0</v>
@@ -7284,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>85</v>
+        <v>88.33333333333333</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="AI42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42" t="b">
         <v>0</v>
@@ -7354,73 +7354,73 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B43" t="n">
-        <v>3.059999942779541</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="C43" t="n">
-        <v>3.539999961853027</v>
+        <v>3.730000019073486</v>
       </c>
       <c r="D43" t="n">
-        <v>2.980000019073486</v>
+        <v>3.444999933242798</v>
       </c>
       <c r="E43" t="n">
-        <v>3.529999971389771</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="F43" t="n">
-        <v>38592800</v>
+        <v>20317900</v>
       </c>
       <c r="G43" t="n">
-        <v>3.553999996185303</v>
+        <v>3.555999994277954</v>
       </c>
       <c r="H43" t="n">
-        <v>4.089499998092651</v>
+        <v>4.044999992847442</v>
       </c>
       <c r="I43" t="n">
-        <v>4.34516666730245</v>
+        <v>4.343000002702078</v>
       </c>
       <c r="J43" t="n">
-        <v>4.738041659196218</v>
+        <v>4.728291660547256</v>
       </c>
       <c r="K43" t="n">
-        <v>5.032624992728233</v>
+        <v>5.022124993801117</v>
       </c>
       <c r="L43" t="n">
-        <v>4.089499998092651</v>
+        <v>4.044999992847442</v>
       </c>
       <c r="M43" t="n">
-        <v>5.011316884376432</v>
+        <v>4.946729336458886</v>
       </c>
       <c r="N43" t="n">
-        <v>3.16768311180887</v>
+        <v>3.143270649235999</v>
       </c>
       <c r="O43" t="n">
-        <v>35.35801849549452</v>
+        <v>41.49822909041876</v>
       </c>
       <c r="P43" t="n">
-        <v>45.08213164023563</v>
+        <v>44.58488727841402</v>
       </c>
       <c r="Q43" t="n">
-        <v>22581195</v>
+        <v>22249615</v>
       </c>
       <c r="R43" t="n">
-        <v>1.709068098477516</v>
+        <v>0.9131798460332909</v>
       </c>
       <c r="S43" t="n">
-        <v>2.023119435579157</v>
+        <v>5.382437925223416</v>
       </c>
       <c r="T43" t="n">
-        <v>1.903564272830039</v>
+        <v>-0.4972443618216147</v>
       </c>
       <c r="U43" t="n">
-        <v>4.408585992751091</v>
+        <v>-1.102974379715949</v>
       </c>
       <c r="V43" t="n">
-        <v>-1.396646742509522</v>
+        <v>6.590258408165917</v>
       </c>
       <c r="W43" t="n">
-        <v>-8.311686783621807</v>
+        <v>0.2695415191491968</v>
       </c>
       <c r="X43" t="b">
         <v>0</v>
@@ -7430,17 +7430,17 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bearish-neutral</t>
         </is>
       </c>
       <c r="AA43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>88.33333333333333</v>
+        <v>87.5</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
@@ -7472,22 +7472,22 @@
         <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO43" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>Expansion with bearish bias</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AR43" t="b">
@@ -7504,79 +7504,79 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>Expansion with bearish bias</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B44" t="n">
-        <v>3.460000038146973</v>
+        <v>3.640000104904175</v>
       </c>
       <c r="C44" t="n">
-        <v>3.730000019073486</v>
+        <v>3.700000047683716</v>
       </c>
       <c r="D44" t="n">
-        <v>3.444999933242798</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="E44" t="n">
-        <v>3.720000028610229</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="F44" t="n">
-        <v>20317900</v>
+        <v>18917500</v>
       </c>
       <c r="G44" t="n">
-        <v>3.555999994277954</v>
+        <v>3.524000024795532</v>
       </c>
       <c r="H44" t="n">
-        <v>4.044999992847442</v>
+        <v>3.967999994754791</v>
       </c>
       <c r="I44" t="n">
-        <v>4.343000002702078</v>
+        <v>4.330500002702077</v>
       </c>
       <c r="J44" t="n">
-        <v>4.728291660547256</v>
+        <v>4.716249996423722</v>
       </c>
       <c r="K44" t="n">
-        <v>5.022124993801117</v>
+        <v>5.008916660149892</v>
       </c>
       <c r="L44" t="n">
-        <v>4.044999992847442</v>
+        <v>3.967999994754791</v>
       </c>
       <c r="M44" t="n">
-        <v>4.946729336458886</v>
+        <v>4.801144944806675</v>
       </c>
       <c r="N44" t="n">
-        <v>3.143270649235999</v>
+        <v>3.134855044702907</v>
       </c>
       <c r="O44" t="n">
-        <v>41.49822909041876</v>
+        <v>35.72758368590998</v>
       </c>
       <c r="P44" t="n">
-        <v>44.58488727841402</v>
+        <v>41.99319310247981</v>
       </c>
       <c r="Q44" t="n">
-        <v>22249615</v>
+        <v>21373760</v>
       </c>
       <c r="R44" t="n">
-        <v>0.9131798460332909</v>
+        <v>0.8850805847918195</v>
       </c>
       <c r="S44" t="n">
-        <v>5.382437925223416</v>
+        <v>-8.064514785188381</v>
       </c>
       <c r="T44" t="n">
-        <v>-0.4972443618216147</v>
+        <v>-2.591694175934201</v>
       </c>
       <c r="U44" t="n">
-        <v>-1.102974379715949</v>
+        <v>-5.812943205957099</v>
       </c>
       <c r="V44" t="n">
-        <v>6.590258408165917</v>
+        <v>-1.156068248902375</v>
       </c>
       <c r="W44" t="n">
-        <v>0.2695415191491968</v>
+        <v>-4.469269576030488</v>
       </c>
       <c r="X44" t="b">
         <v>0</v>
@@ -7586,17 +7586,17 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>Bearish-neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
       </c>
       <c r="AB44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="n">
-        <v>87.5</v>
+        <v>82.5</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
@@ -7616,10 +7616,10 @@
         <v>0</v>
       </c>
       <c r="AI44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44" t="b">
         <v>0</v>
@@ -7628,22 +7628,22 @@
         <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO44" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
       <c r="AR44" t="b">
@@ -7660,79 +7660,79 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B45" t="n">
-        <v>3.640000104904175</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="C45" t="n">
-        <v>3.700000047683716</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="D45" t="n">
-        <v>3.380000114440918</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="E45" t="n">
-        <v>3.420000076293945</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="F45" t="n">
-        <v>18917500</v>
+        <v>14500900</v>
       </c>
       <c r="G45" t="n">
-        <v>3.524000024795532</v>
+        <v>3.508000040054321</v>
       </c>
       <c r="H45" t="n">
-        <v>3.967999994754791</v>
+        <v>3.901999998092651</v>
       </c>
       <c r="I45" t="n">
-        <v>4.330500002702077</v>
+        <v>4.315166672070821</v>
       </c>
       <c r="J45" t="n">
-        <v>4.716249996423722</v>
+        <v>4.705499998728434</v>
       </c>
       <c r="K45" t="n">
-        <v>5.008916660149892</v>
+        <v>4.99758332669735</v>
       </c>
       <c r="L45" t="n">
-        <v>3.967999994754791</v>
+        <v>3.901999998092651</v>
       </c>
       <c r="M45" t="n">
-        <v>4.801144944806675</v>
+        <v>4.688828379319611</v>
       </c>
       <c r="N45" t="n">
-        <v>3.134855044702907</v>
+        <v>3.115171616865691</v>
       </c>
       <c r="O45" t="n">
-        <v>35.72758368590998</v>
+        <v>35.55012427666139</v>
       </c>
       <c r="P45" t="n">
-        <v>41.99319310247981</v>
+        <v>40.32949162540094</v>
       </c>
       <c r="Q45" t="n">
-        <v>21373760</v>
+        <v>21182370</v>
       </c>
       <c r="R45" t="n">
-        <v>0.8850805847918195</v>
+        <v>0.6845740113122375</v>
       </c>
       <c r="S45" t="n">
-        <v>-8.064514785188381</v>
+        <v>-0.2923973754437204</v>
       </c>
       <c r="T45" t="n">
-        <v>-2.591694175934201</v>
+        <v>-1.663701477078874</v>
       </c>
       <c r="U45" t="n">
-        <v>-5.812943205957099</v>
+        <v>-3.961836083811943</v>
       </c>
       <c r="V45" t="n">
-        <v>-1.156068248902375</v>
+        <v>-3.399430213361665</v>
       </c>
       <c r="W45" t="n">
-        <v>-4.469269576030488</v>
+        <v>-2.292261417978436</v>
       </c>
       <c r="X45" t="b">
         <v>0</v>
@@ -7752,7 +7752,7 @@
         <v>1</v>
       </c>
       <c r="AC45" t="n">
-        <v>82.5</v>
+        <v>79.16666666666666</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="b">
         <v>0</v>
@@ -7822,73 +7822,73 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B46" t="n">
-        <v>3.400000095367432</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="C46" t="n">
-        <v>3.559999942779541</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="D46" t="n">
-        <v>3.329999923706055</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="E46" t="n">
-        <v>3.410000085830688</v>
+        <v>3.529999971389771</v>
       </c>
       <c r="F46" t="n">
-        <v>14500900</v>
+        <v>15892600</v>
       </c>
       <c r="G46" t="n">
-        <v>3.508000040054321</v>
+        <v>3.522000026702881</v>
       </c>
       <c r="H46" t="n">
-        <v>3.901999998092651</v>
+        <v>3.848999989032746</v>
       </c>
       <c r="I46" t="n">
-        <v>4.315166672070821</v>
+        <v>4.301166673501332</v>
       </c>
       <c r="J46" t="n">
-        <v>4.705499998728434</v>
+        <v>4.696083333094915</v>
       </c>
       <c r="K46" t="n">
-        <v>4.99758332669735</v>
+        <v>4.987041660149893</v>
       </c>
       <c r="L46" t="n">
-        <v>3.901999998092651</v>
+        <v>3.848999989032746</v>
       </c>
       <c r="M46" t="n">
-        <v>4.688828379319611</v>
+        <v>4.581634682266999</v>
       </c>
       <c r="N46" t="n">
-        <v>3.115171616865691</v>
+        <v>3.116365295798493</v>
       </c>
       <c r="O46" t="n">
-        <v>35.55012427666139</v>
+        <v>39.43757226841189</v>
       </c>
       <c r="P46" t="n">
-        <v>40.32949162540094</v>
+        <v>38.06883322015099</v>
       </c>
       <c r="Q46" t="n">
-        <v>21182370</v>
+        <v>21203790</v>
       </c>
       <c r="R46" t="n">
-        <v>0.6845740113122375</v>
+        <v>0.7495169495642052</v>
       </c>
       <c r="S46" t="n">
-        <v>-0.2923973754437204</v>
+        <v>3.519058138963338</v>
       </c>
       <c r="T46" t="n">
-        <v>-1.663701477078874</v>
+        <v>-2.260658405249956</v>
       </c>
       <c r="U46" t="n">
-        <v>-3.961836083811943</v>
+        <v>-5.6054721102066</v>
       </c>
       <c r="V46" t="n">
-        <v>-3.399430213361665</v>
+        <v>-5.107528380623205</v>
       </c>
       <c r="W46" t="n">
-        <v>-2.292261417978436</v>
+        <v>2.023119435579157</v>
       </c>
       <c r="X46" t="b">
         <v>0</v>
@@ -7908,7 +7908,7 @@
         <v>1</v>
       </c>
       <c r="AC46" t="n">
-        <v>79.16666666666666</v>
+        <v>75</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="AI46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ46" t="b">
         <v>0</v>
@@ -7943,14 +7943,14 @@
         <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO46" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -7978,73 +7978,73 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B47" t="n">
-        <v>3.390000104904175</v>
+        <v>3.910000085830689</v>
       </c>
       <c r="C47" t="n">
-        <v>3.599999904632568</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="D47" t="n">
-        <v>3.380000114440918</v>
+        <v>3.750999927520752</v>
       </c>
       <c r="E47" t="n">
-        <v>3.529999971389771</v>
+        <v>3.769999980926514</v>
       </c>
       <c r="F47" t="n">
-        <v>15892600</v>
+        <v>44549900</v>
       </c>
       <c r="G47" t="n">
-        <v>3.522000026702881</v>
+        <v>3.57000002861023</v>
       </c>
       <c r="H47" t="n">
-        <v>3.848999989032746</v>
+        <v>3.807499992847442</v>
       </c>
       <c r="I47" t="n">
-        <v>4.301166673501332</v>
+        <v>4.290500009059906</v>
       </c>
       <c r="J47" t="n">
-        <v>4.696083333094915</v>
+        <v>4.688916665315628</v>
       </c>
       <c r="K47" t="n">
-        <v>4.987041660149893</v>
+        <v>4.977041659752528</v>
       </c>
       <c r="L47" t="n">
-        <v>3.848999989032746</v>
+        <v>3.807499992847442</v>
       </c>
       <c r="M47" t="n">
-        <v>4.581634682266999</v>
+        <v>4.449433700623677</v>
       </c>
       <c r="N47" t="n">
-        <v>3.116365295798493</v>
+        <v>3.165566285071208</v>
       </c>
       <c r="O47" t="n">
-        <v>39.43757226841189</v>
+        <v>46.40087558679783</v>
       </c>
       <c r="P47" t="n">
-        <v>38.06883322015099</v>
+        <v>33.71943317043392</v>
       </c>
       <c r="Q47" t="n">
-        <v>21203790</v>
+        <v>22638495</v>
       </c>
       <c r="R47" t="n">
-        <v>0.7495169495642052</v>
+        <v>1.967882582300634</v>
       </c>
       <c r="S47" t="n">
-        <v>3.519058138963338</v>
+        <v>6.798867180790791</v>
       </c>
       <c r="T47" t="n">
-        <v>-2.260658405249956</v>
+        <v>-4.349400049717062</v>
       </c>
       <c r="U47" t="n">
-        <v>-5.6054721102066</v>
+        <v>-11.42509418285715</v>
       </c>
       <c r="V47" t="n">
-        <v>-5.107528380623205</v>
+        <v>10.23391511183365</v>
       </c>
       <c r="W47" t="n">
-        <v>2.023119435579157</v>
+        <v>6.798867180790791</v>
       </c>
       <c r="X47" t="b">
         <v>0</v>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AA47" t="b">
@@ -8064,7 +8064,7 @@
         <v>1</v>
       </c>
       <c r="AC47" t="n">
-        <v>75</v>
+        <v>70.83333333333334</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
@@ -8096,17 +8096,17 @@
         <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO47" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8134,73 +8134,73 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B48" t="n">
-        <v>3.910000085830689</v>
+        <v>3.680000066757202</v>
       </c>
       <c r="C48" t="n">
-        <v>4.079999923706055</v>
+        <v>3.789999961853027</v>
       </c>
       <c r="D48" t="n">
-        <v>3.750999927520752</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="E48" t="n">
         <v>3.769999980926514</v>
       </c>
       <c r="F48" t="n">
-        <v>44549900</v>
+        <v>16935000</v>
       </c>
       <c r="G48" t="n">
-        <v>3.57000002861023</v>
+        <v>3.580000019073486</v>
       </c>
       <c r="H48" t="n">
-        <v>3.807499992847442</v>
+        <v>3.772500002384186</v>
       </c>
       <c r="I48" t="n">
-        <v>4.290500009059906</v>
+        <v>4.276166673501333</v>
       </c>
       <c r="J48" t="n">
-        <v>4.688916665315628</v>
+        <v>4.682666665315628</v>
       </c>
       <c r="K48" t="n">
-        <v>4.977041659752528</v>
+        <v>4.96799999276797</v>
       </c>
       <c r="L48" t="n">
-        <v>3.807499992847442</v>
+        <v>3.772500002384186</v>
       </c>
       <c r="M48" t="n">
-        <v>4.449433700623677</v>
+        <v>4.333584476250604</v>
       </c>
       <c r="N48" t="n">
-        <v>3.165566285071208</v>
+        <v>3.211415528517767</v>
       </c>
       <c r="O48" t="n">
-        <v>46.40087558679783</v>
+        <v>46.40087558679784</v>
       </c>
       <c r="P48" t="n">
-        <v>33.71943317043392</v>
+        <v>29.74602907948673</v>
       </c>
       <c r="Q48" t="n">
-        <v>22638495</v>
+        <v>22674620</v>
       </c>
       <c r="R48" t="n">
-        <v>1.967882582300634</v>
+        <v>0.7468702893367122</v>
       </c>
       <c r="S48" t="n">
-        <v>6.798867180790791</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>-4.349400049717062</v>
+        <v>-3.973404090947195</v>
       </c>
       <c r="U48" t="n">
-        <v>-11.42509418285715</v>
+        <v>-11.78372148447376</v>
       </c>
       <c r="V48" t="n">
-        <v>10.23391511183365</v>
+        <v>10.55718140863706</v>
       </c>
       <c r="W48" t="n">
-        <v>6.798867180790791</v>
+        <v>1.344084729347816</v>
       </c>
       <c r="X48" t="b">
         <v>0</v>
@@ -8220,7 +8220,7 @@
         <v>1</v>
       </c>
       <c r="AC48" t="n">
-        <v>70.83333333333334</v>
+        <v>57.49999999999999</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="AI48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="b">
         <v>0</v>
@@ -8255,19 +8255,19 @@
         <v>1</v>
       </c>
       <c r="AN48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO48" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>Bearish trend bias</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AR48" t="b">
@@ -8284,79 +8284,79 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>Bearish trend bias</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B49" t="n">
-        <v>3.680000066757202</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="C49" t="n">
-        <v>3.789999961853027</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="D49" t="n">
         <v>3.569999933242798</v>
       </c>
       <c r="E49" t="n">
-        <v>3.769999980926514</v>
+        <v>3.670000076293946</v>
       </c>
       <c r="F49" t="n">
-        <v>16935000</v>
+        <v>14612400</v>
       </c>
       <c r="G49" t="n">
-        <v>3.580000019073486</v>
+        <v>3.630000019073486</v>
       </c>
       <c r="H49" t="n">
-        <v>3.772500002384186</v>
+        <v>3.739999997615814</v>
       </c>
       <c r="I49" t="n">
-        <v>4.276166673501333</v>
+        <v>4.264666672547659</v>
       </c>
       <c r="J49" t="n">
-        <v>4.682666665315628</v>
+        <v>4.674833331505457</v>
       </c>
       <c r="K49" t="n">
-        <v>4.96799999276797</v>
+        <v>4.956833326816559</v>
       </c>
       <c r="L49" t="n">
-        <v>3.772500002384186</v>
+        <v>3.739999997615814</v>
       </c>
       <c r="M49" t="n">
-        <v>4.333584476250604</v>
+        <v>4.239473358299977</v>
       </c>
       <c r="N49" t="n">
-        <v>3.211415528517767</v>
+        <v>3.240526636931652</v>
       </c>
       <c r="O49" t="n">
-        <v>46.40087558679784</v>
+        <v>43.95849922751746</v>
       </c>
       <c r="P49" t="n">
-        <v>29.74602907948673</v>
+        <v>26.70980540120685</v>
       </c>
       <c r="Q49" t="n">
-        <v>22674620</v>
+        <v>22532445</v>
       </c>
       <c r="R49" t="n">
-        <v>0.7468702893367122</v>
+        <v>0.6485048559976514</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>-2.65251737767892</v>
       </c>
       <c r="T49" t="n">
-        <v>-3.973404090947195</v>
+        <v>-3.036223678279878</v>
       </c>
       <c r="U49" t="n">
-        <v>-11.78372148447376</v>
+        <v>-10.20715629022799</v>
       </c>
       <c r="V49" t="n">
-        <v>10.55718140863706</v>
+        <v>3.966008669656085</v>
       </c>
       <c r="W49" t="n">
-        <v>1.344084729347816</v>
+        <v>7.309941357396421</v>
       </c>
       <c r="X49" t="b">
         <v>0</v>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish-neutral</t>
         </is>
       </c>
       <c r="AA49" t="b">
@@ -8376,7 +8376,7 @@
         <v>1</v>
       </c>
       <c r="AC49" t="n">
-        <v>57.49999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK49" t="b">
         <v>0</v>
@@ -8408,22 +8408,22 @@
         <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO49" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
       <c r="AR49" t="b">
@@ -8440,79 +8440,79 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish trend bias</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B50" t="n">
-        <v>3.650000095367432</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="C50" t="n">
-        <v>3.720000028610229</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="D50" t="n">
-        <v>3.569999933242798</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="E50" t="n">
-        <v>3.670000076293946</v>
+        <v>3.630000114440918</v>
       </c>
       <c r="F50" t="n">
-        <v>14612400</v>
+        <v>14003600</v>
       </c>
       <c r="G50" t="n">
-        <v>3.630000019073486</v>
+        <v>3.674000024795532</v>
       </c>
       <c r="H50" t="n">
-        <v>3.739999997615814</v>
+        <v>3.712000000476837</v>
       </c>
       <c r="I50" t="n">
-        <v>4.264666672547659</v>
+        <v>4.253166671593984</v>
       </c>
       <c r="J50" t="n">
-        <v>4.674833331505457</v>
+        <v>4.666583333412806</v>
       </c>
       <c r="K50" t="n">
-        <v>4.956833326816559</v>
+        <v>4.943458326657614</v>
       </c>
       <c r="L50" t="n">
-        <v>3.739999997615814</v>
+        <v>3.712000000476837</v>
       </c>
       <c r="M50" t="n">
-        <v>4.239473358299977</v>
+        <v>4.16596955765604</v>
       </c>
       <c r="N50" t="n">
-        <v>3.240526636931652</v>
+        <v>3.258030443297634</v>
       </c>
       <c r="O50" t="n">
-        <v>43.95849922751746</v>
+        <v>42.98387621106848</v>
       </c>
       <c r="P50" t="n">
-        <v>26.70980540120685</v>
+        <v>24.4595666552202</v>
       </c>
       <c r="Q50" t="n">
-        <v>22532445</v>
+        <v>22244155</v>
       </c>
       <c r="R50" t="n">
-        <v>0.6485048559976514</v>
+        <v>0.6295406591079769</v>
       </c>
       <c r="S50" t="n">
-        <v>-2.65251737767892</v>
+        <v>-1.089917194045964</v>
       </c>
       <c r="T50" t="n">
-        <v>-3.036223678279878</v>
+        <v>-2.250238745986646</v>
       </c>
       <c r="U50" t="n">
-        <v>-10.20715629022799</v>
+        <v>-8.424766531189221</v>
       </c>
       <c r="V50" t="n">
-        <v>3.966008669656085</v>
+        <v>-3.713524328750506</v>
       </c>
       <c r="W50" t="n">
-        <v>7.309941357396421</v>
+        <v>6.451613579846494</v>
       </c>
       <c r="X50" t="b">
         <v>0</v>
@@ -8532,7 +8532,7 @@
         <v>1</v>
       </c>
       <c r="AC50" t="n">
-        <v>47.5</v>
+        <v>40</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="b">
         <v>0</v>
@@ -8602,73 +8602,73 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B51" t="n">
-        <v>3.480000019073486</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="C51" t="n">
-        <v>3.710000038146973</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="D51" t="n">
-        <v>3.460000038146973</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="E51" t="n">
-        <v>3.630000114440918</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="F51" t="n">
-        <v>14003600</v>
+        <v>12569200</v>
       </c>
       <c r="G51" t="n">
-        <v>3.674000024795532</v>
+        <v>3.676000022888183</v>
       </c>
       <c r="H51" t="n">
-        <v>3.712000000476837</v>
+        <v>3.680000007152558</v>
       </c>
       <c r="I51" t="n">
-        <v>4.253166671593984</v>
+        <v>4.234500006834666</v>
       </c>
       <c r="J51" t="n">
-        <v>4.666583333412806</v>
+        <v>4.656916668017705</v>
       </c>
       <c r="K51" t="n">
-        <v>4.943458326657614</v>
+        <v>4.931583327054978</v>
       </c>
       <c r="L51" t="n">
-        <v>3.712000000476837</v>
+        <v>3.680000007152558</v>
       </c>
       <c r="M51" t="n">
-        <v>4.16596955765604</v>
+        <v>4.082361428205009</v>
       </c>
       <c r="N51" t="n">
-        <v>3.258030443297634</v>
+        <v>3.277638586100106</v>
       </c>
       <c r="O51" t="n">
-        <v>42.98387621106848</v>
+        <v>40.79237770649166</v>
       </c>
       <c r="P51" t="n">
-        <v>24.4595666552202</v>
+        <v>21.86746849295706</v>
       </c>
       <c r="Q51" t="n">
-        <v>22244155</v>
+        <v>22000425</v>
       </c>
       <c r="R51" t="n">
-        <v>0.6295406591079769</v>
+        <v>0.5713162359363513</v>
       </c>
       <c r="S51" t="n">
-        <v>-1.089917194045964</v>
+        <v>-2.479342968333542</v>
       </c>
       <c r="T51" t="n">
-        <v>-2.250238745986646</v>
+        <v>-2.592098162263145</v>
       </c>
       <c r="U51" t="n">
-        <v>-8.424766531189221</v>
+        <v>-10.59748195379387</v>
       </c>
       <c r="V51" t="n">
-        <v>-3.713524328750506</v>
+        <v>-6.100796292761823</v>
       </c>
       <c r="W51" t="n">
-        <v>6.451613579846494</v>
+        <v>0.2832858511134795</v>
       </c>
       <c r="X51" t="b">
         <v>0</v>
@@ -8688,7 +8688,7 @@
         <v>1</v>
       </c>
       <c r="AC51" t="n">
-        <v>40</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK51" t="b">
         <v>0</v>
@@ -8723,10 +8723,10 @@
         <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO51" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -8758,73 +8758,73 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B52" t="n">
-        <v>3.460000038146973</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="C52" t="n">
-        <v>3.609999895095825</v>
+        <v>3.759999990463257</v>
       </c>
       <c r="D52" t="n">
-        <v>3.440000057220459</v>
+        <v>3.529999971389771</v>
       </c>
       <c r="E52" t="n">
-        <v>3.539999961853027</v>
+        <v>3.640000104904175</v>
       </c>
       <c r="F52" t="n">
-        <v>12569200</v>
+        <v>16256000</v>
       </c>
       <c r="G52" t="n">
-        <v>3.676000022888183</v>
+        <v>3.650000047683716</v>
       </c>
       <c r="H52" t="n">
-        <v>3.680000007152558</v>
+        <v>3.657000017166138</v>
       </c>
       <c r="I52" t="n">
-        <v>4.234500006834666</v>
+        <v>4.213166673978169</v>
       </c>
       <c r="J52" t="n">
-        <v>4.656916668017705</v>
+        <v>4.649416669209798</v>
       </c>
       <c r="K52" t="n">
-        <v>4.931583327054978</v>
+        <v>4.919333327809969</v>
       </c>
       <c r="L52" t="n">
-        <v>3.680000007152558</v>
+        <v>3.657000017166138</v>
       </c>
       <c r="M52" t="n">
-        <v>4.082361428205009</v>
+        <v>4.00752442880287</v>
       </c>
       <c r="N52" t="n">
-        <v>3.277638586100106</v>
+        <v>3.306475605529406</v>
       </c>
       <c r="O52" t="n">
-        <v>40.79237770649166</v>
+        <v>44.19675078654147</v>
       </c>
       <c r="P52" t="n">
-        <v>21.86746849295706</v>
+        <v>19.17005250157796</v>
       </c>
       <c r="Q52" t="n">
-        <v>22000425</v>
+        <v>21638400</v>
       </c>
       <c r="R52" t="n">
-        <v>0.5713162359363513</v>
+        <v>0.75125702454895</v>
       </c>
       <c r="S52" t="n">
-        <v>-2.479342968333542</v>
+        <v>2.824862828495678</v>
       </c>
       <c r="T52" t="n">
-        <v>-2.592098162263145</v>
+        <v>-2.697415991379096</v>
       </c>
       <c r="U52" t="n">
-        <v>-10.59748195379387</v>
+        <v>-12.33529154162433</v>
       </c>
       <c r="V52" t="n">
-        <v>-6.100796292761823</v>
+        <v>-0.8174378955344785</v>
       </c>
       <c r="W52" t="n">
-        <v>0.2832858511134795</v>
+        <v>-3.448272590982615</v>
       </c>
       <c r="X52" t="b">
         <v>0</v>
@@ -8844,18 +8844,18 @@
         <v>1</v>
       </c>
       <c r="AC52" t="n">
-        <v>26.66666666666667</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Tight</t>
         </is>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
       <c r="AF52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
@@ -8864,10 +8864,10 @@
         <v>0</v>
       </c>
       <c r="AI52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="b">
         <v>0</v>
@@ -8879,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO52" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>Bearish trend bias</t>
+          <t>Tight range with bearish bias</t>
         </is>
       </c>
       <c r="AR52" t="b">
@@ -8908,79 +8908,79 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>Bearish trend bias</t>
+          <t>Tight range with bearish bias</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B53" t="n">
-        <v>3.599999904632568</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="C53" t="n">
-        <v>3.759999990463257</v>
+        <v>3.680000066757202</v>
       </c>
       <c r="D53" t="n">
-        <v>3.529999971389771</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="E53" t="n">
-        <v>3.640000104904175</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="F53" t="n">
-        <v>16256000</v>
+        <v>14054500</v>
       </c>
       <c r="G53" t="n">
-        <v>3.650000047683716</v>
+        <v>3.604000043869018</v>
       </c>
       <c r="H53" t="n">
-        <v>3.657000017166138</v>
+        <v>3.639000010490418</v>
       </c>
       <c r="I53" t="n">
-        <v>4.213166673978169</v>
+        <v>4.193666672706604</v>
       </c>
       <c r="J53" t="n">
-        <v>4.649416669209798</v>
+        <v>4.638500003019969</v>
       </c>
       <c r="K53" t="n">
-        <v>4.919333327809969</v>
+        <v>4.907083327571551</v>
       </c>
       <c r="L53" t="n">
-        <v>3.657000017166138</v>
+        <v>3.639000010490418</v>
       </c>
       <c r="M53" t="n">
-        <v>4.00752442880287</v>
+        <v>3.973594799234242</v>
       </c>
       <c r="N53" t="n">
-        <v>3.306475605529406</v>
+        <v>3.304405221746594</v>
       </c>
       <c r="O53" t="n">
-        <v>44.19675078654147</v>
+        <v>41.61958724298763</v>
       </c>
       <c r="P53" t="n">
-        <v>19.17005250157796</v>
+        <v>18.38938102661515</v>
       </c>
       <c r="Q53" t="n">
-        <v>21638400</v>
+        <v>20499330</v>
       </c>
       <c r="R53" t="n">
-        <v>0.75125702454895</v>
+        <v>0.6856077735223541</v>
       </c>
       <c r="S53" t="n">
-        <v>2.824862828495678</v>
+        <v>-2.74725659805386</v>
       </c>
       <c r="T53" t="n">
-        <v>-2.697415991379096</v>
+        <v>-0.7806714749628121</v>
       </c>
       <c r="U53" t="n">
-        <v>-12.33529154162433</v>
+        <v>-4.07234917535334</v>
       </c>
       <c r="V53" t="n">
-        <v>-0.8174378955344785</v>
+        <v>-2.479342968333542</v>
       </c>
       <c r="W53" t="n">
-        <v>-3.448272590982615</v>
+        <v>-6.100796292761823</v>
       </c>
       <c r="X53" t="b">
         <v>0</v>
@@ -9000,7 +9000,7 @@
         <v>1</v>
       </c>
       <c r="AC53" t="n">
-        <v>13.33333333333333</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
@@ -9020,10 +9020,10 @@
         <v>0</v>
       </c>
       <c r="AI53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK53" t="b">
         <v>0</v>
@@ -9070,73 +9070,73 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B54" t="n">
-        <v>3.549999952316284</v>
+        <v>3.470000028610229</v>
       </c>
       <c r="C54" t="n">
-        <v>3.680000066757202</v>
+        <v>3.529999971389771</v>
       </c>
       <c r="D54" t="n">
+        <v>3.380000114440918</v>
+      </c>
+      <c r="E54" t="n">
         <v>3.460000038146973</v>
       </c>
-      <c r="E54" t="n">
-        <v>3.539999961853027</v>
-      </c>
       <c r="F54" t="n">
-        <v>14054500</v>
+        <v>12183800</v>
       </c>
       <c r="G54" t="n">
-        <v>3.604000043869018</v>
+        <v>3.562000036239624</v>
       </c>
       <c r="H54" t="n">
-        <v>3.639000010490418</v>
+        <v>3.634000015258789</v>
       </c>
       <c r="I54" t="n">
-        <v>4.193666672706604</v>
+        <v>4.171000003814697</v>
       </c>
       <c r="J54" t="n">
-        <v>4.638500003019969</v>
+        <v>4.627083337306976</v>
       </c>
       <c r="K54" t="n">
-        <v>4.907083327571551</v>
+        <v>4.893666661779085</v>
       </c>
       <c r="L54" t="n">
-        <v>3.639000010490418</v>
+        <v>3.634000015258789</v>
       </c>
       <c r="M54" t="n">
-        <v>3.973594799234242</v>
+        <v>3.976461669036351</v>
       </c>
       <c r="N54" t="n">
-        <v>3.304405221746594</v>
+        <v>3.291538361481227</v>
       </c>
       <c r="O54" t="n">
-        <v>41.61958724298763</v>
+        <v>39.62875048549894</v>
       </c>
       <c r="P54" t="n">
-        <v>18.38938102661515</v>
+        <v>18.84764184587788</v>
       </c>
       <c r="Q54" t="n">
-        <v>20499330</v>
+        <v>19077160</v>
       </c>
       <c r="R54" t="n">
-        <v>0.6856077735223541</v>
+        <v>0.6386590037510824</v>
       </c>
       <c r="S54" t="n">
-        <v>-2.74725659805386</v>
+        <v>-2.259884874805995</v>
       </c>
       <c r="T54" t="n">
-        <v>-0.7806714749628121</v>
+        <v>0.4582608192627298</v>
       </c>
       <c r="U54" t="n">
-        <v>-4.07234917535334</v>
+        <v>2.491986101106303</v>
       </c>
       <c r="V54" t="n">
-        <v>-2.479342968333542</v>
+        <v>-2.259884874805995</v>
       </c>
       <c r="W54" t="n">
-        <v>-6.100796292761823</v>
+        <v>-5.722071765160186</v>
       </c>
       <c r="X54" t="b">
         <v>0</v>
@@ -9146,17 +9146,17 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>Bearish-neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
       </c>
       <c r="AB54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>10.83333333333333</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
@@ -9191,14 +9191,14 @@
         <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO54" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -9226,73 +9226,73 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B55" t="n">
-        <v>3.470000028610229</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="C55" t="n">
-        <v>3.529999971389771</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="D55" t="n">
-        <v>3.380000114440918</v>
+        <v>3.289999961853027</v>
       </c>
       <c r="E55" t="n">
-        <v>3.460000038146973</v>
+        <v>3.509999990463257</v>
       </c>
       <c r="F55" t="n">
-        <v>12183800</v>
+        <v>12799000</v>
       </c>
       <c r="G55" t="n">
-        <v>3.562000036239624</v>
+        <v>3.538000011444092</v>
       </c>
       <c r="H55" t="n">
-        <v>3.634000015258789</v>
+        <v>3.610500013828278</v>
       </c>
       <c r="I55" t="n">
-        <v>4.171000003814697</v>
+        <v>4.150000003973643</v>
       </c>
       <c r="J55" t="n">
-        <v>4.627083337306976</v>
+        <v>4.616583337386449</v>
       </c>
       <c r="K55" t="n">
-        <v>4.893666661779085</v>
+        <v>4.879999995231628</v>
       </c>
       <c r="L55" t="n">
-        <v>3.634000015258789</v>
+        <v>3.610500013828278</v>
       </c>
       <c r="M55" t="n">
-        <v>3.976461669036351</v>
+        <v>3.915440017462521</v>
       </c>
       <c r="N55" t="n">
-        <v>3.291538361481227</v>
+        <v>3.305560010194034</v>
       </c>
       <c r="O55" t="n">
-        <v>39.62875048549894</v>
+        <v>41.51183822050004</v>
       </c>
       <c r="P55" t="n">
-        <v>18.84764184587788</v>
+        <v>16.89184337162819</v>
       </c>
       <c r="Q55" t="n">
-        <v>19077160</v>
+        <v>18403455</v>
       </c>
       <c r="R55" t="n">
-        <v>0.6386590037510824</v>
+        <v>0.6954672369943579</v>
       </c>
       <c r="S55" t="n">
-        <v>-2.259884874805995</v>
+        <v>1.445085311127969</v>
       </c>
       <c r="T55" t="n">
-        <v>0.4582608192627298</v>
+        <v>-1.955798474249693</v>
       </c>
       <c r="U55" t="n">
-        <v>2.491986101106303</v>
+        <v>-10.37688688188566</v>
       </c>
       <c r="V55" t="n">
-        <v>-2.259884874805995</v>
+        <v>-3.57143161248179</v>
       </c>
       <c r="W55" t="n">
-        <v>-5.722071765160186</v>
+        <v>-3.305788435109824</v>
       </c>
       <c r="X55" t="b">
         <v>0</v>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bearish-neutral</t>
         </is>
       </c>
       <c r="AA55" t="b">
@@ -9312,15 +9312,15 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>14.16666666666667</v>
+        <v>10</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Tight</t>
+          <t>Squeeze</t>
         </is>
       </c>
       <c r="AE55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF55" t="b">
         <v>1</v>
@@ -9335,7 +9335,7 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="b">
         <v>0</v>
@@ -9347,19 +9347,19 @@
         <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO55" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>Tight range with bearish bias</t>
+          <t>Squeeze watch</t>
         </is>
       </c>
       <c r="AR55" t="b">
@@ -9376,79 +9376,79 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>Tight range with bearish bias</t>
+          <t>Squeeze watch</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B56" t="n">
-        <v>3.329999923706055</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="C56" t="n">
-        <v>3.539999961853027</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="D56" t="n">
-        <v>3.289999961853027</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="E56" t="n">
-        <v>3.509999990463257</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="F56" t="n">
-        <v>12799000</v>
+        <v>10074000</v>
       </c>
       <c r="G56" t="n">
-        <v>3.538000011444092</v>
+        <v>3.518000030517578</v>
       </c>
       <c r="H56" t="n">
-        <v>3.610500013828278</v>
+        <v>3.583500015735626</v>
       </c>
       <c r="I56" t="n">
-        <v>4.150000003973643</v>
+        <v>4.127833338578542</v>
       </c>
       <c r="J56" t="n">
-        <v>4.616583337386449</v>
+        <v>4.604916669925054</v>
       </c>
       <c r="K56" t="n">
-        <v>4.879999995231628</v>
+        <v>4.867124994595845</v>
       </c>
       <c r="L56" t="n">
-        <v>3.610500013828278</v>
+        <v>3.583500015735626</v>
       </c>
       <c r="M56" t="n">
-        <v>3.915440017462521</v>
+        <v>3.842914299729459</v>
       </c>
       <c r="N56" t="n">
-        <v>3.305560010194034</v>
+        <v>3.324085731741794</v>
       </c>
       <c r="O56" t="n">
-        <v>41.51183822050004</v>
+        <v>39.64731871459451</v>
       </c>
       <c r="P56" t="n">
-        <v>16.89184337162819</v>
+        <v>14.47826330987637</v>
       </c>
       <c r="Q56" t="n">
-        <v>18403455</v>
+        <v>18197975</v>
       </c>
       <c r="R56" t="n">
-        <v>0.6954672369943579</v>
+        <v>0.5535780766816089</v>
       </c>
       <c r="S56" t="n">
-        <v>1.445085311127969</v>
+        <v>-1.994300097805957</v>
       </c>
       <c r="T56" t="n">
-        <v>-1.955798474249693</v>
+        <v>-2.413580061751821</v>
       </c>
       <c r="U56" t="n">
-        <v>-10.37688688188566</v>
+        <v>-14.28843500766595</v>
       </c>
       <c r="V56" t="n">
-        <v>-3.57143161248179</v>
+        <v>-2.8248560935075</v>
       </c>
       <c r="W56" t="n">
-        <v>-3.305788435109824</v>
+        <v>-2.8248560935075</v>
       </c>
       <c r="X56" t="b">
         <v>0</v>
@@ -9458,14 +9458,14 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>Bearish-neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
       </c>
       <c r="AB56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO56" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -9538,73 +9538,73 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B57" t="n">
-        <v>3.490000009536743</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="C57" t="n">
-        <v>3.569999933242798</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="D57" t="n">
-        <v>3.400000095367432</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="E57" t="n">
-        <v>3.440000057220459</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="F57" t="n">
-        <v>10074000</v>
+        <v>14397900</v>
       </c>
       <c r="G57" t="n">
-        <v>3.518000030517578</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="H57" t="n">
-        <v>3.583500015735626</v>
+        <v>3.563500022888184</v>
       </c>
       <c r="I57" t="n">
-        <v>4.127833338578542</v>
+        <v>4.109000007311503</v>
       </c>
       <c r="J57" t="n">
-        <v>4.604916669925054</v>
+        <v>4.594416670004526</v>
       </c>
       <c r="K57" t="n">
-        <v>4.867124994595845</v>
+        <v>4.855791661143303</v>
       </c>
       <c r="L57" t="n">
-        <v>3.583500015735626</v>
+        <v>3.563500022888184</v>
       </c>
       <c r="M57" t="n">
-        <v>3.842914299729459</v>
+        <v>3.796762904825005</v>
       </c>
       <c r="N57" t="n">
-        <v>3.324085731741794</v>
+        <v>3.330237140951363</v>
       </c>
       <c r="O57" t="n">
-        <v>39.64731871459451</v>
+        <v>40.06149716614433</v>
       </c>
       <c r="P57" t="n">
-        <v>14.47826330987637</v>
+        <v>13.09178506741042</v>
       </c>
       <c r="Q57" t="n">
-        <v>18197975</v>
+        <v>18361535</v>
       </c>
       <c r="R57" t="n">
-        <v>0.5535780766816089</v>
+        <v>0.7841337883788039</v>
       </c>
       <c r="S57" t="n">
-        <v>-1.994300097805957</v>
+        <v>0.2906973923522793</v>
       </c>
       <c r="T57" t="n">
-        <v>-2.413580061751821</v>
+        <v>-1.38647824246595</v>
       </c>
       <c r="U57" t="n">
-        <v>-14.28843500766595</v>
+        <v>-9.576274535082963</v>
       </c>
       <c r="V57" t="n">
-        <v>-2.8248560935075</v>
+        <v>-0.2890170622255939</v>
       </c>
       <c r="W57" t="n">
-        <v>-2.8248560935075</v>
+        <v>-5.21978164133764</v>
       </c>
       <c r="X57" t="b">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bearish-neutral</t>
         </is>
       </c>
       <c r="AA57" t="b">
@@ -9624,7 +9624,7 @@
         <v>1</v>
       </c>
       <c r="AC57" t="n">
-        <v>10</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
@@ -9659,10 +9659,10 @@
         <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO57" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -9694,73 +9694,73 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B58" t="n">
-        <v>3.440000057220459</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="C58" t="n">
-        <v>3.559999942779541</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="D58" t="n">
-        <v>3.339999914169312</v>
+        <v>3.220000028610229</v>
       </c>
       <c r="E58" t="n">
-        <v>3.450000047683716</v>
+        <v>3.289999961853027</v>
       </c>
       <c r="F58" t="n">
-        <v>14397900</v>
+        <v>18345400</v>
       </c>
       <c r="G58" t="n">
-        <v>3.480000019073486</v>
+        <v>3.430000019073487</v>
       </c>
       <c r="H58" t="n">
-        <v>3.563500022888184</v>
+        <v>3.542500019073486</v>
       </c>
       <c r="I58" t="n">
-        <v>4.109000007311503</v>
+        <v>4.091666674613952</v>
       </c>
       <c r="J58" t="n">
-        <v>4.594416670004526</v>
+        <v>4.58075000445048</v>
       </c>
       <c r="K58" t="n">
-        <v>4.855791661143303</v>
+        <v>4.844624995191892</v>
       </c>
       <c r="L58" t="n">
-        <v>3.563500022888184</v>
+        <v>3.542500019073486</v>
       </c>
       <c r="M58" t="n">
-        <v>3.796762904825005</v>
+        <v>3.795055377522433</v>
       </c>
       <c r="N58" t="n">
-        <v>3.330237140951363</v>
+        <v>3.28994466062454</v>
       </c>
       <c r="O58" t="n">
-        <v>40.06149716614433</v>
+        <v>35.82521351685349</v>
       </c>
       <c r="P58" t="n">
-        <v>13.09178506741042</v>
+        <v>14.2585946133601</v>
       </c>
       <c r="Q58" t="n">
-        <v>18361535</v>
+        <v>18076545</v>
       </c>
       <c r="R58" t="n">
-        <v>0.7841337883788039</v>
+        <v>1.014873140857393</v>
       </c>
       <c r="S58" t="n">
-        <v>0.2906973923522793</v>
+        <v>-4.637683583167207</v>
       </c>
       <c r="T58" t="n">
-        <v>-1.38647824246595</v>
+        <v>1.166809545949688</v>
       </c>
       <c r="U58" t="n">
-        <v>-9.576274535082963</v>
+        <v>8.912532095063529</v>
       </c>
       <c r="V58" t="n">
-        <v>-0.2890170622255939</v>
+        <v>-6.26780709994228</v>
       </c>
       <c r="W58" t="n">
-        <v>-5.21978164133764</v>
+        <v>-7.062146968756933</v>
       </c>
       <c r="X58" t="b">
         <v>0</v>
@@ -9770,14 +9770,14 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Bearish-neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
       </c>
       <c r="AB58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>9.166666666666666</v>
@@ -9803,7 +9803,7 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK58" t="b">
         <v>0</v>
@@ -9815,14 +9815,14 @@
         <v>0</v>
       </c>
       <c r="AN58" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO58" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -9850,73 +9850,73 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B59" t="n">
-        <v>3.400000095367432</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="C59" t="n">
-        <v>3.400000095367432</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="D59" t="n">
-        <v>3.220000028610229</v>
+        <v>3.345000028610229</v>
       </c>
       <c r="E59" t="n">
-        <v>3.289999961853027</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="F59" t="n">
-        <v>18345400</v>
+        <v>14409900</v>
       </c>
       <c r="G59" t="n">
-        <v>3.430000019073487</v>
+        <v>3.422000026702881</v>
       </c>
       <c r="H59" t="n">
-        <v>3.542500019073486</v>
+        <v>3.534500026702881</v>
       </c>
       <c r="I59" t="n">
-        <v>4.091666674613952</v>
+        <v>4.078666679064432</v>
       </c>
       <c r="J59" t="n">
-        <v>4.58075000445048</v>
+        <v>4.568333339691162</v>
       </c>
       <c r="K59" t="n">
-        <v>4.844624995191892</v>
+        <v>4.834666662414869</v>
       </c>
       <c r="L59" t="n">
-        <v>3.542500019073486</v>
+        <v>3.534500026702881</v>
       </c>
       <c r="M59" t="n">
-        <v>3.795055377522433</v>
+        <v>3.792139100525568</v>
       </c>
       <c r="N59" t="n">
-        <v>3.28994466062454</v>
+        <v>3.276860952880194</v>
       </c>
       <c r="O59" t="n">
-        <v>35.82521351685349</v>
+        <v>41.26020061219845</v>
       </c>
       <c r="P59" t="n">
-        <v>14.2585946133601</v>
+        <v>14.57853002553365</v>
       </c>
       <c r="Q59" t="n">
-        <v>18076545</v>
+        <v>17844465</v>
       </c>
       <c r="R59" t="n">
-        <v>1.014873140857393</v>
+        <v>0.8075277123746776</v>
       </c>
       <c r="S59" t="n">
-        <v>-4.637683583167207</v>
+        <v>3.951371305417828</v>
       </c>
       <c r="T59" t="n">
-        <v>1.166809545949688</v>
+        <v>0.3199354121735496</v>
       </c>
       <c r="U59" t="n">
-        <v>8.912532095063529</v>
+        <v>2.243807477868653</v>
       </c>
       <c r="V59" t="n">
-        <v>-6.26780709994228</v>
+        <v>-0.5813947847045586</v>
       </c>
       <c r="W59" t="n">
-        <v>-7.062146968756933</v>
+        <v>-1.156068248902375</v>
       </c>
       <c r="X59" t="b">
         <v>0</v>
@@ -9926,17 +9926,17 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bearish-neutral</t>
         </is>
       </c>
       <c r="AA59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB59" t="b">
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
@@ -9956,10 +9956,10 @@
         <v>0</v>
       </c>
       <c r="AI59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK59" t="b">
         <v>0</v>
@@ -9971,19 +9971,19 @@
         <v>0</v>
       </c>
       <c r="AN59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO59" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>Squeeze watch</t>
+          <t>Squeeze release watch (bearish bias)</t>
         </is>
       </c>
       <c r="AR59" t="b">
@@ -10000,79 +10000,79 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>Squeeze watch</t>
+          <t>Squeeze release watch (bearish bias)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B60" t="n">
-        <v>3.349999904632568</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="C60" t="n">
-        <v>3.519999980926514</v>
+        <v>3.505000114440918</v>
       </c>
       <c r="D60" t="n">
-        <v>3.345000028610229</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="E60" t="n">
-        <v>3.420000076293945</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="F60" t="n">
-        <v>14378800</v>
+        <v>10458300</v>
       </c>
       <c r="G60" t="n">
-        <v>3.422000026702881</v>
+        <v>3.398000049591064</v>
       </c>
       <c r="H60" t="n">
-        <v>3.534500026702881</v>
+        <v>3.529500031471252</v>
       </c>
       <c r="I60" t="n">
-        <v>4.078666679064432</v>
+        <v>4.06516668399175</v>
       </c>
       <c r="J60" t="n">
-        <v>4.568333339691162</v>
+        <v>4.555083340406417</v>
       </c>
       <c r="K60" t="n">
-        <v>4.834666662414869</v>
+        <v>4.826749996344248</v>
       </c>
       <c r="L60" t="n">
-        <v>3.534500026702881</v>
+        <v>3.529500031471252</v>
       </c>
       <c r="M60" t="n">
-        <v>3.792139100525568</v>
+        <v>3.794550161997429</v>
       </c>
       <c r="N60" t="n">
-        <v>3.276860952880194</v>
+        <v>3.264449900945076</v>
       </c>
       <c r="O60" t="n">
-        <v>41.26020061219845</v>
+        <v>40.4096868236392</v>
       </c>
       <c r="P60" t="n">
-        <v>14.57853002553365</v>
+        <v>15.0191317842653</v>
       </c>
       <c r="Q60" t="n">
-        <v>17842910</v>
+        <v>17559330</v>
       </c>
       <c r="R60" t="n">
-        <v>0.8058550987479061</v>
+        <v>0.5955978958194874</v>
       </c>
       <c r="S60" t="n">
-        <v>3.951371305417828</v>
+        <v>-0.8771921263311722</v>
       </c>
       <c r="T60" t="n">
-        <v>0.3199354121735496</v>
+        <v>0.4406017587316455</v>
       </c>
       <c r="U60" t="n">
-        <v>2.243807477868653</v>
+        <v>3.022264645063322</v>
       </c>
       <c r="V60" t="n">
-        <v>-0.5813947847045586</v>
+        <v>-1.73912875218144</v>
       </c>
       <c r="W60" t="n">
-        <v>-1.156068248902375</v>
+        <v>-3.418800167667357</v>
       </c>
       <c r="X60" t="b">
         <v>0</v>
@@ -10112,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="AI60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="b">
         <v>0</v>
@@ -10162,73 +10162,73 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B61" t="n">
-        <v>3.450000047683716</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="C61" t="n">
-        <v>3.503999948501587</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="D61" t="n">
-        <v>3.369999885559082</v>
+        <v>3.359999895095825</v>
       </c>
       <c r="E61" t="n">
-        <v>3.390000104904175</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="F61" t="n">
-        <v>10223619</v>
+        <v>10278571</v>
       </c>
       <c r="G61" t="n">
-        <v>3.398000049591064</v>
+        <v>3.394000053405762</v>
       </c>
       <c r="H61" t="n">
-        <v>3.529500031471252</v>
+        <v>3.527500033378601</v>
       </c>
       <c r="I61" t="n">
-        <v>4.06516668399175</v>
+        <v>4.044166688124339</v>
       </c>
       <c r="J61" t="n">
-        <v>4.555083340406417</v>
+        <v>4.543500008185704</v>
       </c>
       <c r="K61" t="n">
-        <v>4.826749996344248</v>
+        <v>4.819770830869675</v>
       </c>
       <c r="L61" t="n">
-        <v>3.529500031471252</v>
+        <v>3.527500033378601</v>
       </c>
       <c r="M61" t="n">
-        <v>3.794550161997429</v>
+        <v>3.795347184135609</v>
       </c>
       <c r="N61" t="n">
-        <v>3.264449900945076</v>
+        <v>3.259652882621593</v>
       </c>
       <c r="O61" t="n">
-        <v>40.4096868236392</v>
+        <v>41.70380785416495</v>
       </c>
       <c r="P61" t="n">
-        <v>15.0191317842653</v>
+        <v>15.18623094103658</v>
       </c>
       <c r="Q61" t="n">
-        <v>17546040.95</v>
+        <v>17207458.55</v>
       </c>
       <c r="R61" t="n">
-        <v>0.5826738367437813</v>
+        <v>0.5973323120397694</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.8771921263311722</v>
+        <v>0.8849548808677277</v>
       </c>
       <c r="T61" t="n">
-        <v>0.4406017587316455</v>
+        <v>0.1670991567712807</v>
       </c>
       <c r="U61" t="n">
-        <v>3.022264645063322</v>
+        <v>1.112575341714095</v>
       </c>
       <c r="V61" t="n">
-        <v>-1.73912875218144</v>
+        <v>3.951371305417828</v>
       </c>
       <c r="W61" t="n">
-        <v>-3.418800167667357</v>
+        <v>-0.5813947847045586</v>
       </c>
       <c r="X61" t="b">
         <v>0</v>
@@ -10327,7 +10327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13224,7 +13224,7 @@
         <v>41.26020061219845</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8058550987479061</v>
+        <v>0.8075277123746776</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>40.4096868236392</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5826738367437813</v>
+        <v>0.5955978958194874</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -13267,6 +13267,41 @@
         </is>
       </c>
       <c r="I84" t="inlineStr">
+        <is>
+          <t>squeeze 이후 밴드폭 확대</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Squeeze release</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3.420000076293945</v>
+      </c>
+      <c r="D85" t="n">
+        <v>15.18623094103658</v>
+      </c>
+      <c r="E85" t="n">
+        <v>10</v>
+      </c>
+      <c r="F85" t="n">
+        <v>41.70380785416495</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.5973323120397694</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Squeeze release watch (bearish bias)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
         <is>
           <t>squeeze 이후 밴드폭 확대</t>
         </is>
@@ -13306,10 +13341,10 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>기준일은 2026-03-16 입니다.
-종가는 3.39, 볼린저 밴드폭은 15.02% 입니다.
+          <t>기준일은 2026-03-17 입니다.
+종가는 3.42, 볼린저 밴드폭은 15.19% 입니다.
 최근 120거래일 기준 밴드폭 percentile은 10.00% 이고, squeeze 수준은 'Squeeze' 입니다.
-RSI(14)는 40.41, 거래량 비율은 0.58배 입니다.
+RSI(14)는 41.70, 거래량 비율은 0.60배 입니다.
 bull score는 0, bear score는 4, score diff는 -4 입니다.
 현재 최종 신호는 'Squeeze release watch (bearish bias)' 이며 강도는 'Moderate' 입니다.
 현재는 변동성 압축 구간 또는 압축 해제 직전 구간으로, 방향성이 정해지기 전 에너지가 축적되는 단계로 해석됩니다.
@@ -13325,12 +13360,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>최근 20거래일 구간은 2026-02-17 부터 2026-03-16 까지입니다.
-종가는 3.46 에서 3.39 로 변했고, 누적 변화율은 -2.02% 입니다.
-같은 기간 볼린저 밴드폭은 43.18% 에서 15.02% 로 변했고, 변화율은 -65.22% 입니다.
+          <t>최근 20거래일 구간은 2026-02-18 부터 2026-03-17 까지입니다.
+종가는 3.53 에서 3.42 로 변했고, 누적 변화율은 -3.12% 입니다.
+같은 기간 볼린저 밴드폭은 45.08% 에서 15.19% 로 변했고, 변화율은 -66.31% 입니다.
 구간 내 가격 범위는 3.29 ~ 3.77 이며, 고저 범위는 약 14.59% 입니다.
-평균 거래량 비율은 0.84배, 평균 RSI는 40.26 입니다.
-squeeze 일수는 6일, tight 구간 일수는 9일, 상단 돌파는 0회, 하단 이탈은 0회 입니다.
+평균 거래량 비율은 0.83배, 평균 RSI는 40.70 입니다.
+squeeze 일수는 7일, tight 구간 일수는 10일, 상단 돌파는 0회, 하단 이탈은 0회 입니다.
 가장 자주 등장한 최종 신호는 'Bearish trend bias' 입니다.
 최근 구간에서 밴드폭이 뚜렷하게 축소되어 변동성 압축이 진행된 것으로 해석됩니다.
 구간의 상당 부분이 squeeze 상태였으므로 에너지 축적 또는 박스권 압축 구간일 가능성이 높습니다.
@@ -13349,8 +13384,8 @@
         <is>
           <t>최근 이벤트 로그 기준으로 마지막 30개 이벤트를 검토했습니다.
 'Squeeze' 는 12회 발생했습니다.
-'Bullish breakout candidate' 는 6회 발생했습니다.
-'Squeeze release' 는 5회 발생했습니다.
+'Squeeze release' 는 6회 발생했습니다.
+'Bullish breakout candidate' 는 5회 발생했습니다.
 'Bullish breakout confirmed' 는 2회 발생했습니다.
 'Failed bullish breakout' 는 2회 발생했습니다.
 'Bearish breakdown candidate' 는 2회 발생했습니다.
@@ -13400,7 +13435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV501"/>
+  <dimension ref="A1:AV502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89396,7 +89431,7 @@
         <v>3.420000076293945</v>
       </c>
       <c r="F500" t="n">
-        <v>14378800</v>
+        <v>14409900</v>
       </c>
       <c r="G500" t="n">
         <v>3.422000026702881</v>
@@ -89429,10 +89464,10 @@
         <v>14.57853002553365</v>
       </c>
       <c r="Q500" t="n">
-        <v>17842910</v>
+        <v>17844465</v>
       </c>
       <c r="R500" t="n">
-        <v>0.8058550987479061</v>
+        <v>0.8075277123746776</v>
       </c>
       <c r="S500" t="n">
         <v>3.951371305417828</v>
@@ -89543,7 +89578,7 @@
         <v>3.450000047683716</v>
       </c>
       <c r="C501" t="n">
-        <v>3.503999948501587</v>
+        <v>3.505000114440918</v>
       </c>
       <c r="D501" t="n">
         <v>3.369999885559082</v>
@@ -89552,7 +89587,7 @@
         <v>3.390000104904175</v>
       </c>
       <c r="F501" t="n">
-        <v>10223619</v>
+        <v>10458300</v>
       </c>
       <c r="G501" t="n">
         <v>3.398000049591064</v>
@@ -89585,10 +89620,10 @@
         <v>15.0191317842653</v>
       </c>
       <c r="Q501" t="n">
-        <v>17546040.95</v>
+        <v>17559330</v>
       </c>
       <c r="R501" t="n">
-        <v>0.5826738367437813</v>
+        <v>0.5955978958194874</v>
       </c>
       <c r="S501" t="n">
         <v>-0.8771921263311722</v>
@@ -89686,6 +89721,162 @@
         <v>0</v>
       </c>
       <c r="AV501" t="inlineStr">
+        <is>
+          <t>Squeeze release watch (bearish bias)</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B502" t="n">
+        <v>3.390000104904175</v>
+      </c>
+      <c r="C502" t="n">
+        <v>3.480000019073486</v>
+      </c>
+      <c r="D502" t="n">
+        <v>3.359999895095825</v>
+      </c>
+      <c r="E502" t="n">
+        <v>3.420000076293945</v>
+      </c>
+      <c r="F502" t="n">
+        <v>10278571</v>
+      </c>
+      <c r="G502" t="n">
+        <v>3.394000053405762</v>
+      </c>
+      <c r="H502" t="n">
+        <v>3.527500033378601</v>
+      </c>
+      <c r="I502" t="n">
+        <v>4.044166688124339</v>
+      </c>
+      <c r="J502" t="n">
+        <v>4.543500008185704</v>
+      </c>
+      <c r="K502" t="n">
+        <v>4.819770830869675</v>
+      </c>
+      <c r="L502" t="n">
+        <v>3.527500033378601</v>
+      </c>
+      <c r="M502" t="n">
+        <v>3.795347184135609</v>
+      </c>
+      <c r="N502" t="n">
+        <v>3.259652882621593</v>
+      </c>
+      <c r="O502" t="n">
+        <v>41.70380785416495</v>
+      </c>
+      <c r="P502" t="n">
+        <v>15.18623094103658</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>17207458.55</v>
+      </c>
+      <c r="R502" t="n">
+        <v>0.5973323120397694</v>
+      </c>
+      <c r="S502" t="n">
+        <v>0.8849548808677277</v>
+      </c>
+      <c r="T502" t="n">
+        <v>0.1670991567712807</v>
+      </c>
+      <c r="U502" t="n">
+        <v>1.112575341714095</v>
+      </c>
+      <c r="V502" t="n">
+        <v>3.951371305417828</v>
+      </c>
+      <c r="W502" t="n">
+        <v>-0.5813947847045586</v>
+      </c>
+      <c r="X502" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y502" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z502" t="inlineStr">
+        <is>
+          <t>Bearish-neutral</t>
+        </is>
+      </c>
+      <c r="AA502" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC502" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD502" t="inlineStr">
+        <is>
+          <t>Squeeze</t>
+        </is>
+      </c>
+      <c r="AE502" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF502" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM502" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN502" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO502" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AP502" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="AQ502" t="inlineStr">
+        <is>
+          <t>Squeeze release watch (bearish bias)</t>
+        </is>
+      </c>
+      <c r="AR502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU502" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV502" t="inlineStr">
         <is>
           <t>Squeeze release watch (bearish bias)</t>
         </is>
